--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>14067875</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>6.05399990081787</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>5.86199998855591</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.8899998664856</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>6.03599977493286</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>4182115</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>6.05800008773804</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>5.96000003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>6.00600004196167</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>6.02799987792969</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>6779050</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>6.13800001144409</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>5.94199991226196</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>6.10599994659424</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>6.02199983596802</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>5756273</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>6.07800006866455</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>5.92799997329712</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>5.92799997329712</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>2721711</v>
+        <v>4023397</v>
       </c>
       <c r="C2715" t="n">
-        <v>5.78800010681152</v>
+        <v>5.76000022888184</v>
       </c>
       <c r="D2715" t="n">
-        <v>5.71199989318848</v>
+        <v>5.67600011825562</v>
       </c>
       <c r="E2715" t="n">
-        <v>5.71999979019165</v>
+        <v>5.75</v>
       </c>
       <c r="F2715" t="n">
-        <v>5.76800012588501</v>
+        <v>5.71600008010864</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>4341971</v>
+        <v>2721711</v>
       </c>
       <c r="C2716" t="n">
-        <v>5.78200006484985</v>
+        <v>5.78800010681152</v>
       </c>
       <c r="D2716" t="n">
-        <v>5.7039999961853</v>
+        <v>5.71199989318848</v>
       </c>
       <c r="E2716" t="n">
-        <v>5.72200012207031</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="F2716" t="n">
-        <v>5.72599983215332</v>
+        <v>5.76800012588501</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>4680439</v>
+        <v>4341971</v>
       </c>
       <c r="C2717" t="n">
         <v>5.78200006484985</v>
       </c>
       <c r="D2717" t="n">
-        <v>5.68599987030029</v>
+        <v>5.7039999961853</v>
       </c>
       <c r="E2717" t="n">
-        <v>5.73199987411499</v>
+        <v>5.72200012207031</v>
       </c>
       <c r="F2717" t="n">
-        <v>5.74399995803833</v>
+        <v>5.72599983215332</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2766970</v>
+        <v>4680439</v>
       </c>
       <c r="C2718" t="n">
-        <v>5.80600023269653</v>
+        <v>5.78200006484985</v>
       </c>
       <c r="D2718" t="n">
-        <v>5.72200012207031</v>
+        <v>5.68599987030029</v>
       </c>
       <c r="E2718" t="n">
-        <v>5.76999998092651</v>
+        <v>5.73199987411499</v>
       </c>
       <c r="F2718" t="n">
-        <v>5.72200012207031</v>
+        <v>5.74399995803833</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>14067875</v>
+        <v>2766970</v>
       </c>
       <c r="C2719" t="n">
-        <v>6.05399990081787</v>
+        <v>5.80600023269653</v>
       </c>
       <c r="D2719" t="n">
-        <v>5.86199998855591</v>
+        <v>5.72200012207031</v>
       </c>
       <c r="E2719" t="n">
-        <v>5.8899998664856</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="F2719" t="n">
-        <v>6.03599977493286</v>
+        <v>5.72200012207031</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>4182115</v>
+        <v>14067875</v>
       </c>
       <c r="C2720" t="n">
-        <v>6.05800008773804</v>
+        <v>6.05399990081787</v>
       </c>
       <c r="D2720" t="n">
-        <v>5.96000003814697</v>
+        <v>5.86199998855591</v>
       </c>
       <c r="E2720" t="n">
-        <v>6.00600004196167</v>
+        <v>5.8899998664856</v>
       </c>
       <c r="F2720" t="n">
-        <v>6.02799987792969</v>
+        <v>6.03599977493286</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>6779050</v>
+        <v>4182115</v>
       </c>
       <c r="C2721" t="n">
-        <v>6.13800001144409</v>
+        <v>6.05800008773804</v>
       </c>
       <c r="D2721" t="n">
-        <v>5.94199991226196</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="E2721" t="n">
-        <v>6.10599994659424</v>
+        <v>6.00600004196167</v>
       </c>
       <c r="F2721" t="n">
-        <v>6.02199983596802</v>
+        <v>6.02799987792969</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>5756273</v>
+        <v>6779050</v>
       </c>
       <c r="C2722" t="n">
-        <v>6.07800006866455</v>
+        <v>6.13800001144409</v>
       </c>
       <c r="D2722" t="n">
-        <v>5.92799997329712</v>
+        <v>5.94199991226196</v>
       </c>
       <c r="E2722" t="n">
-        <v>6.05999994277954</v>
+        <v>6.10599994659424</v>
       </c>
       <c r="F2722" t="n">
-        <v>5.92799997329712</v>
+        <v>6.02199983596802</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>7909045</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>5.93400001525879</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>5.86999988555908</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>5.88000011444092</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>5.89799976348877</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60396003723145</v>
+        <v>3.60396027565002</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.8824999332428</v>
       </c>
       <c r="G4" t="n">
-        <v>3.54911231994629</v>
+        <v>3.54911208152771</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.78250002861023</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45769929885864</v>
+        <v>3.45769906044006</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>3.57425117492676</v>
+        <v>3.5742506980896</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62909865379333</v>
+        <v>3.62909913063049</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>3.51940298080444</v>
+        <v>3.51940274238586</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.75250005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43027496337891</v>
+        <v>3.43027520179749</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.84249997138977</v>
       </c>
       <c r="G13" t="n">
-        <v>3.51254677772522</v>
+        <v>3.51254725456238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G14" t="n">
-        <v>3.38228297233582</v>
+        <v>3.38228344917297</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.77749991416931</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45312833786011</v>
+        <v>3.45312809944153</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.83750009536743</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50797629356384</v>
+        <v>3.50797605514526</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.8824999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>3.54911231994629</v>
+        <v>3.54911208152771</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>3.58796310424805</v>
+        <v>3.58796215057373</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>3.51483225822449</v>
+        <v>3.51483273506165</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03249979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6862313747406</v>
+        <v>3.68623161315918</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>3.66566395759583</v>
+        <v>3.66566371917725</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G23" t="n">
-        <v>3.65195202827454</v>
+        <v>3.65195178985596</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57425117492676</v>
+        <v>3.5742506980896</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G25" t="n">
-        <v>3.41884851455688</v>
+        <v>3.41884899139404</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G28" t="n">
-        <v>3.28172898292542</v>
+        <v>3.28172922134399</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G30" t="n">
-        <v>3.17203330993652</v>
+        <v>3.17203307151794</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.52250003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.22002553939819</v>
+        <v>3.22002530097961</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G33" t="n">
-        <v>3.19488596916199</v>
+        <v>3.19488644599915</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.27258706092834</v>
+        <v>3.27258801460266</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.62750005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>3.3160092830658</v>
+        <v>3.31600904464722</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.62249994277954</v>
       </c>
       <c r="G38" t="n">
-        <v>3.3114378452301</v>
+        <v>3.31143832206726</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>3.27258706092834</v>
+        <v>3.27258801460266</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35485935211182</v>
+        <v>3.3548595905304</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G41" t="n">
-        <v>3.33200597763062</v>
+        <v>3.33200621604919</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.625</v>
       </c>
       <c r="G42" t="n">
-        <v>3.31372332572937</v>
+        <v>3.31372356414795</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75250005722046</v>
       </c>
       <c r="G43" t="n">
-        <v>3.43027496337891</v>
+        <v>3.43027520179749</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>3.5513973236084</v>
+        <v>3.55139756202698</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.89249992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.55825328826904</v>
+        <v>3.55825352668762</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>3.51026177406311</v>
+        <v>3.51026153564453</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>3.56053900718689</v>
+        <v>3.56053876876831</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.58339214324951</v>
+        <v>3.58339190483093</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G51" t="n">
-        <v>3.63366937637329</v>
+        <v>3.63366913795471</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.26249980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89648222923279</v>
+        <v>3.89648151397705</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.31750011444092</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94675874710083</v>
+        <v>3.94675993919373</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.36250019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.9878945350647</v>
+        <v>3.98789501190186</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G57" t="n">
-        <v>3.98103809356689</v>
+        <v>3.98103833198547</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>3.97646880149841</v>
+        <v>3.97646808624268</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>3.99018001556396</v>
+        <v>3.99018049240112</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.39249992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>4.01531887054443</v>
+        <v>4.01531744003296</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.35249996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>3.97875356674194</v>
+        <v>3.97875261306763</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G65" t="n">
-        <v>4.02217531204224</v>
+        <v>4.02217435836792</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>3.96275639533997</v>
+        <v>3.96275615692139</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>3.96275639533997</v>
+        <v>3.96275615692139</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G68" t="n">
-        <v>3.93990278244019</v>
+        <v>3.93990302085876</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.375</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99932074546814</v>
+        <v>3.9993212223053</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>3.93533158302307</v>
+        <v>3.93533229827881</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.25</v>
       </c>
       <c r="G71" t="n">
-        <v>3.88505482673645</v>
+        <v>3.88505554199219</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.25250005722046</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8873405456543</v>
+        <v>3.88734006881714</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.34250020980835</v>
       </c>
       <c r="G76" t="n">
-        <v>3.96961283683777</v>
+        <v>3.96961212158203</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.36749982833862</v>
       </c>
       <c r="G77" t="n">
-        <v>3.99246644973755</v>
+        <v>3.99246573448181</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94904470443726</v>
+        <v>3.94904494285583</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>3.89876651763916</v>
+        <v>3.89876747131348</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.93990278244019</v>
+        <v>3.93990302085876</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.33750009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>3.96504187583923</v>
+        <v>3.9650411605835</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G84" t="n">
-        <v>3.85306072235107</v>
+        <v>3.85306096076965</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.17749977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>3.81878042221069</v>
+        <v>3.81878018379211</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.23250007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.86905789375305</v>
+        <v>3.86905813217163</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.25750017166138</v>
       </c>
       <c r="G89" t="n">
-        <v>3.89191102981567</v>
+        <v>3.89191150665283</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.39750003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>4.01988935470581</v>
+        <v>4.01988887786865</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.30249977111816</v>
       </c>
       <c r="G92" t="n">
-        <v>3.93304657936096</v>
+        <v>3.93304634094238</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.90790891647339</v>
+        <v>3.90790939331055</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>3.92161965370178</v>
+        <v>3.92161989212036</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G97" t="n">
-        <v>3.83477807044983</v>
+        <v>3.83477783203125</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.83455610275269</v>
+        <v>3.83455634117126</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.29250001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.96622443199158</v>
+        <v>3.96622490882874</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>4.02397346496582</v>
+        <v>4.02397394180298</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G103" t="n">
-        <v>4.01473426818848</v>
+        <v>4.01473379135132</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.35249996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.0216646194458</v>
+        <v>4.02166318893433</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>4.03783369064331</v>
+        <v>4.03783321380615</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>4.02859449386597</v>
+        <v>4.02859401702881</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.03783369064331</v>
+        <v>4.03783321380615</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.37249994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>4.04014444351196</v>
+        <v>4.04014301300049</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.35750007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>4.02628421783447</v>
+        <v>4.02628374099731</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G111" t="n">
-        <v>4.05169486999512</v>
+        <v>4.05169343948364</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>4.01935386657715</v>
+        <v>4.01935338973999</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.16249990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.8461058139801</v>
+        <v>3.84610557556152</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G115" t="n">
-        <v>3.79759693145752</v>
+        <v>3.7975971698761</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.12750005722046</v>
       </c>
       <c r="G118" t="n">
-        <v>3.81376624107361</v>
+        <v>3.81376600265503</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.125</v>
       </c>
       <c r="G119" t="n">
-        <v>3.81145620346069</v>
+        <v>3.81145644187927</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.27250003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>3.94774460792542</v>
+        <v>3.94774436950684</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89923501014709</v>
+        <v>3.89923548698425</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.3274998664856</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99856448173523</v>
+        <v>3.99856400489807</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G124" t="n">
-        <v>3.8276264667511</v>
+        <v>3.82762622833252</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>3.82993578910828</v>
+        <v>3.82993626594543</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.35750007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>4.02628421783447</v>
+        <v>4.02628374099731</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.4225001335144</v>
       </c>
       <c r="G130" t="n">
-        <v>4.08634376525879</v>
+        <v>4.08634328842163</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G131" t="n">
-        <v>4.0701732635498</v>
+        <v>4.07017278671265</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.26749992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>3.94312500953674</v>
+        <v>3.94312477111816</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G133" t="n">
-        <v>3.98239421844482</v>
+        <v>3.98239493370056</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.37249994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>4.04014444351196</v>
+        <v>4.04014301300049</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>4.09789323806763</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G137" t="n">
-        <v>4.01473426818848</v>
+        <v>4.01473379135132</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07941341400146</v>
+        <v>4.07941293716431</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>4.1209921836853</v>
+        <v>4.12099313735962</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.49749994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15564250946045</v>
+        <v>4.15564203262329</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.22725105285645</v>
+        <v>4.2272515296936</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>4.23187208175659</v>
+        <v>4.23187112808228</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G148" t="n">
-        <v>4.22263240814209</v>
+        <v>4.22263193130493</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.61749982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>4.26652097702026</v>
+        <v>4.26652145385742</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.8125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.4466986656189</v>
+        <v>4.44669818878174</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.8125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.4466986656189</v>
+        <v>4.44669818878174</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G154" t="n">
-        <v>4.45362949371338</v>
+        <v>4.45362997055054</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>4.37046957015991</v>
+        <v>4.37046909332275</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.41204977035522</v>
+        <v>4.41205024719238</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.75</v>
       </c>
       <c r="G157" t="n">
-        <v>4.38894939422607</v>
+        <v>4.38894987106323</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G158" t="n">
-        <v>4.59222745895386</v>
+        <v>4.5922269821167</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>4.60146760940552</v>
+        <v>4.6014666557312</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.90749979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>4.53447771072388</v>
+        <v>4.53447818756104</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.52754783630371</v>
+        <v>4.52754878997803</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.875</v>
       </c>
       <c r="G166" t="n">
-        <v>4.50444841384888</v>
+        <v>4.50444793701172</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.875</v>
       </c>
       <c r="G167" t="n">
-        <v>4.50444841384888</v>
+        <v>4.50444793701172</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>4.55064868927002</v>
+        <v>4.55064821243286</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.95749998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.58067750930786</v>
+        <v>4.5806770324707</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.87750005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>4.50675821304321</v>
+        <v>4.50675773620605</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>4.63380670547485</v>
+        <v>4.63380718231201</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.98250007629395</v>
       </c>
       <c r="G174" t="n">
-        <v>4.6037769317627</v>
+        <v>4.60377788543701</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>4.60146760940552</v>
+        <v>4.6014666557312</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G177" t="n">
-        <v>4.53216886520386</v>
+        <v>4.5321683883667</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.78249979019165</v>
       </c>
       <c r="G178" t="n">
-        <v>4.41897964477539</v>
+        <v>4.41897916793823</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>4.3658504486084</v>
+        <v>4.36584997177124</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.80249977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>4.43745803833008</v>
+        <v>4.43745899200439</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>4.42359924316406</v>
+        <v>4.42359972000122</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G184" t="n">
-        <v>4.44900846481323</v>
+        <v>4.44900989532471</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.95749998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>4.58067750930786</v>
+        <v>4.5806770324707</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>4.66152667999268</v>
+        <v>4.66152715682983</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>4.64304685592651</v>
+        <v>4.64304637908936</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>4.63380670547485</v>
+        <v>4.63380718231201</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51830816268921</v>
+        <v>4.51830863952637</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>4.49982786178589</v>
+        <v>4.49982833862305</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>4.40742969512939</v>
+        <v>4.40742921829224</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G199" t="n">
-        <v>4.42359924316406</v>
+        <v>4.42359972000122</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G202" t="n">
-        <v>4.37970972061157</v>
+        <v>4.37970876693726</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.84749984741211</v>
       </c>
       <c r="G203" t="n">
-        <v>4.47903871536255</v>
+        <v>4.47903776168823</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.7975001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>4.43283891677856</v>
+        <v>4.43283939361572</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>4.42359924316406</v>
+        <v>4.42359972000122</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G209" t="n">
-        <v>4.30117130279541</v>
+        <v>4.30117082595825</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>4.30579090118408</v>
+        <v>4.30579042434692</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.2688307762146</v>
+        <v>4.26883125305176</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>4.24111175537109</v>
+        <v>4.24111127853394</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>4.09789323806763</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.52250003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>4.17874240875244</v>
+        <v>4.1787428855896</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>3.89461541175842</v>
+        <v>3.894615650177</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>3.97315526008606</v>
+        <v>3.9731547832489</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.39750003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>4.0632438659668</v>
+        <v>4.06324338912964</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G226" t="n">
-        <v>3.9569845199585</v>
+        <v>3.95698475837708</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.40250015258789</v>
       </c>
       <c r="G227" t="n">
-        <v>4.06786251068115</v>
+        <v>4.06786346435547</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.4225001335144</v>
       </c>
       <c r="G228" t="n">
-        <v>4.08634376525879</v>
+        <v>4.08634328842163</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>4.09789323806763</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.44750022888184</v>
       </c>
       <c r="G230" t="n">
-        <v>4.10944271087646</v>
+        <v>4.10944318771362</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>4.12561321258545</v>
+        <v>4.12561225891113</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G233" t="n">
-        <v>4.18567180633545</v>
+        <v>4.18567276000977</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.48250007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>4.14178276062012</v>
+        <v>4.14178228378296</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>4.20415163040161</v>
+        <v>4.20415210723877</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>4.1209921836853</v>
+        <v>4.12099313735962</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>4.23187208175659</v>
+        <v>4.23187112808228</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.52750015258789</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18336248397827</v>
+        <v>4.18336200714111</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>4.25497102737427</v>
+        <v>4.25497150421143</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.65250015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>4.29886102676392</v>
+        <v>4.29886054992676</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>4.2688307762146</v>
+        <v>4.26883125305176</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G245" t="n">
-        <v>4.30579090118408</v>
+        <v>4.30579042434692</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G246" t="n">
-        <v>4.22494173049927</v>
+        <v>4.22494125366211</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>4.21339130401611</v>
+        <v>4.21339225769043</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>4.23649215698242</v>
+        <v>4.23649168014526</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>4.30579090118408</v>
+        <v>4.30579042434692</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.60750007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>4.25728130340576</v>
+        <v>4.2572808265686</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.2688307762146</v>
+        <v>4.26883125305176</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>4.24111175537109</v>
+        <v>4.24111127853394</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G255" t="n">
-        <v>4.28269147872925</v>
+        <v>4.28269100189209</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.27807140350342</v>
+        <v>4.27807092666626</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.32427024841309</v>
+        <v>4.32427072525024</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>4.27807140350342</v>
+        <v>4.27807092666626</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>4.29655170440674</v>
+        <v>4.29655075073242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>4.30579090118408</v>
+        <v>4.30579042434692</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>4.30117130279541</v>
+        <v>4.30117082595825</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G264" t="n">
-        <v>4.30117130279541</v>
+        <v>4.30117082595825</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.6875</v>
       </c>
       <c r="G265" t="n">
-        <v>4.33120059967041</v>
+        <v>4.33120107650757</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G267" t="n">
-        <v>4.30579090118408</v>
+        <v>4.30579042434692</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.66249990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>4.30810117721558</v>
+        <v>4.30810070037842</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.65749979019165</v>
       </c>
       <c r="G269" t="n">
-        <v>4.30348014831543</v>
+        <v>4.30348062515259</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G270" t="n">
-        <v>4.40280914306641</v>
+        <v>4.40280961990356</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G271" t="n">
-        <v>4.44900846481323</v>
+        <v>4.44900989532471</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.75250005722046</v>
       </c>
       <c r="G272" t="n">
-        <v>4.39125967025757</v>
+        <v>4.39126014709473</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.71750020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.35892057418823</v>
+        <v>4.35892009735107</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>4.40049934387207</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>4.40049934387207</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>4.40049934387207</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G279" t="n">
-        <v>4.28731107711792</v>
+        <v>4.28731155395508</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>4.31965112686157</v>
+        <v>4.31965017318726</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>4.40742969512939</v>
+        <v>4.40742921829224</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G286" t="n">
-        <v>4.4259090423584</v>
+        <v>4.42590999603271</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.82250022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>4.45593881607056</v>
+        <v>4.45593929290771</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.82250022888184</v>
       </c>
       <c r="G289" t="n">
-        <v>4.45593881607056</v>
+        <v>4.45593929290771</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>4.4259090423584</v>
+        <v>4.42590999603271</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.83750009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>4.46979904174805</v>
+        <v>4.46979856491089</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G294" t="n">
-        <v>4.51368761062622</v>
+        <v>4.51368856430054</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G295" t="n">
-        <v>4.51368761062622</v>
+        <v>4.51368856430054</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>4.45362949371338</v>
+        <v>4.45362997055054</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.87750005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>4.50675821304321</v>
+        <v>4.50675773620605</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>4.41204977035522</v>
+        <v>4.41205024719238</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.85249996185303</v>
       </c>
       <c r="G301" t="n">
-        <v>4.48365926742554</v>
+        <v>4.48365831375122</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.87249994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>4.50213813781738</v>
+        <v>4.50213861465454</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.85249996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>4.48365926742554</v>
+        <v>4.48365831375122</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>4.46748828887939</v>
+        <v>4.46748924255371</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.80249977111816</v>
       </c>
       <c r="G305" t="n">
-        <v>4.43745803833008</v>
+        <v>4.43745899200439</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G306" t="n">
-        <v>4.43976879119873</v>
+        <v>4.43976926803589</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.88749980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.51599836349487</v>
+        <v>4.51599788665771</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.875</v>
       </c>
       <c r="G308" t="n">
-        <v>4.50444841384888</v>
+        <v>4.50444793701172</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G309" t="n">
-        <v>4.49982786178589</v>
+        <v>4.49982833862305</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.52754783630371</v>
+        <v>4.52754878997803</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.96250009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>4.58529806137085</v>
+        <v>4.58529853820801</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>4.67076587677002</v>
+        <v>4.67076635360718</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>4.68462657928467</v>
+        <v>4.68462705612183</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G314" t="n">
-        <v>4.67076587677002</v>
+        <v>4.67076635360718</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>4.66152667999268</v>
+        <v>4.66152715682983</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.125</v>
       </c>
       <c r="G316" t="n">
-        <v>4.73544502258301</v>
+        <v>4.73544597625732</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.125</v>
       </c>
       <c r="G317" t="n">
-        <v>4.73544502258301</v>
+        <v>4.73544597625732</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>4.75854539871216</v>
+        <v>4.75854635238647</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>4.87404441833496</v>
+        <v>4.8740439414978</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>5.02188205718994</v>
+        <v>5.0218825340271</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04498243331909</v>
+        <v>5.04498195648193</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>4.92024374008179</v>
+        <v>4.92024326324463</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.95258378982544</v>
+        <v>4.95258283615112</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G330" t="n">
-        <v>4.95720243453979</v>
+        <v>4.95720338821411</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>4.92024374008179</v>
+        <v>4.92024326324463</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.86480474472046</v>
+        <v>4.86480379104614</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G333" t="n">
-        <v>4.90176439285278</v>
+        <v>4.90176343917847</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.25</v>
       </c>
       <c r="G334" t="n">
-        <v>4.85094499588013</v>
+        <v>4.85094451904297</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>4.89252328872681</v>
+        <v>4.89252424240112</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.09580230712891</v>
+        <v>5.09580135345459</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G338" t="n">
-        <v>5.06808280944824</v>
+        <v>5.06808185577393</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.5</v>
       </c>
       <c r="G339" t="n">
-        <v>5.08194208145142</v>
+        <v>5.08194160461426</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>5.04498243331909</v>
+        <v>5.04498195648193</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.5</v>
       </c>
       <c r="G343" t="n">
-        <v>5.08194208145142</v>
+        <v>5.08194160461426</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G344" t="n">
-        <v>5.17434120178223</v>
+        <v>5.17434072494507</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G345" t="n">
-        <v>5.1096625328064</v>
+        <v>5.10966110229492</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>5.33603858947754</v>
+        <v>5.33603954315186</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>5.58551597595215</v>
+        <v>5.58551645278931</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>5.51621723175049</v>
+        <v>5.51621675491333</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>5.53931665420532</v>
+        <v>5.53931713104248</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G350" t="n">
-        <v>5.57627582550049</v>
+        <v>5.57627630233765</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G351" t="n">
-        <v>5.59937572479248</v>
+        <v>5.59937620162964</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G352" t="n">
-        <v>5.4931173324585</v>
+        <v>5.49311637878418</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>5.52083730697632</v>
+        <v>5.520836353302</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>5.63633489608765</v>
+        <v>5.63633632659912</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G355" t="n">
-        <v>5.6084098815918</v>
+        <v>5.60841035842896</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>5.65495204925537</v>
+        <v>5.65495252609253</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.66426086425781</v>
+        <v>5.66426134109497</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093826293945</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G367" t="n">
-        <v>5.84577894210815</v>
+        <v>5.84577798843384</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>5.66891574859619</v>
+        <v>5.66891527175903</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64564371109009</v>
+        <v>5.6456446647644</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G376" t="n">
-        <v>5.84112405776978</v>
+        <v>5.84112358093262</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>5.89232063293457</v>
+        <v>5.89232158660889</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G379" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G380" t="n">
-        <v>5.82716035842896</v>
+        <v>5.82716083526611</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>5.82250595092773</v>
+        <v>5.82250642776489</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G383" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>5.74338293075562</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>5.79923486709595</v>
+        <v>5.79923534393311</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>5.74338293075562</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734567642212</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G391" t="n">
-        <v>5.68753290176392</v>
+        <v>5.68753337860107</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>5.79923486709595</v>
+        <v>5.79923534393311</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.76665592193604</v>
+        <v>5.76665544509888</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>5.74803781509399</v>
+        <v>5.74803829193115</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>5.84112405776978</v>
+        <v>5.84112358093262</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>5.82250595092773</v>
+        <v>5.82250642776489</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>5.85508728027344</v>
+        <v>5.85508632659912</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G408" t="n">
-        <v>5.74803781509399</v>
+        <v>5.74803829193115</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G409" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218635559082</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G410" t="n">
-        <v>5.65960741043091</v>
+        <v>5.65960693359375</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>5.56652164459229</v>
+        <v>5.56652069091797</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G414" t="n">
-        <v>5.57582950592041</v>
+        <v>5.57582998275757</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G418" t="n">
-        <v>5.66891574859619</v>
+        <v>5.66891527175903</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G419" t="n">
-        <v>5.64564371109009</v>
+        <v>5.6456446647644</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>6.13500022888184</v>
       </c>
       <c r="G420" t="n">
-        <v>5.71080446243286</v>
+        <v>5.71080493927002</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G422" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218635559082</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G423" t="n">
-        <v>5.66426086425781</v>
+        <v>5.66426134109497</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>5.58048295974731</v>
+        <v>5.58048439025879</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>5.65960741043091</v>
+        <v>5.65960693359375</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G428" t="n">
-        <v>5.65029811859131</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64564371109009</v>
+        <v>5.6456446647644</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.125</v>
       </c>
       <c r="G430" t="n">
-        <v>5.70149517059326</v>
+        <v>5.70149564743042</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68753290176392</v>
+        <v>5.68753337860107</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>5.74338293075562</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G437" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>5.65960741043091</v>
+        <v>5.65960693359375</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.125</v>
       </c>
       <c r="G440" t="n">
-        <v>5.70149517059326</v>
+        <v>5.70149564743042</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>5.68287897109985</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.68287897109985</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218635559082</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G444" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6.2350001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>5.80388975143433</v>
+        <v>5.80388927459717</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>5.79923486709595</v>
+        <v>5.79923534393311</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G449" t="n">
-        <v>5.74338293075562</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G453" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734567642212</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>6.2350001335144</v>
       </c>
       <c r="G455" t="n">
-        <v>5.80388975143433</v>
+        <v>5.80388927459717</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G456" t="n">
-        <v>5.88301229476929</v>
+        <v>5.88301277160645</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05522108078003</v>
+        <v>6.05522060394287</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G459" t="n">
-        <v>6.19019460678101</v>
+        <v>6.19019556045532</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>6.04591274261475</v>
+        <v>6.04591131210327</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>6.03194952011108</v>
+        <v>6.03194856643677</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>6.0133318901062</v>
+        <v>6.01333236694336</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>6.0738377571106</v>
+        <v>6.07383823394775</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>6.05522108078003</v>
+        <v>6.05522060394287</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>6.02264022827148</v>
+        <v>6.02264070510864</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>6.2460470199585</v>
+        <v>6.24604606628418</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G469" t="n">
-        <v>6.31120538711548</v>
+        <v>6.31120681762695</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>6.40429067611694</v>
+        <v>6.40429210662842</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>6.32516956329346</v>
+        <v>6.3251690864563</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>6.21346569061279</v>
+        <v>6.21346664428711</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>6.38102006912231</v>
+        <v>6.38102054595947</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>6.24139165878296</v>
+        <v>6.24139213562012</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>6.08314609527588</v>
+        <v>6.08314561843872</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G478" t="n">
-        <v>6.02264022827148</v>
+        <v>6.02264070510864</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>5.99937009811401</v>
+        <v>5.99936962127686</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G481" t="n">
-        <v>5.94817209243774</v>
+        <v>5.94817304611206</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G482" t="n">
-        <v>5.99471521377563</v>
+        <v>5.99471473693848</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>6.05522108078003</v>
+        <v>6.05522060394287</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>6.01798582077026</v>
+        <v>6.01798725128174</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>5.91559171676636</v>
+        <v>5.91559267044067</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G487" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351768493652</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G488" t="n">
-        <v>6.01798582077026</v>
+        <v>6.01798725128174</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>6.00402402877808</v>
+        <v>6.00402307510376</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>5.97144365310669</v>
+        <v>5.97144317626953</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>5.99006032943726</v>
+        <v>5.99006080627441</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>6.00402402877808</v>
+        <v>6.00402307510376</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G495" t="n">
-        <v>6.06452941894531</v>
+        <v>6.06452894210815</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G496" t="n">
-        <v>6.12038040161133</v>
+        <v>6.12037944793701</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G498" t="n">
-        <v>6.15296030044556</v>
+        <v>6.15296125411987</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G499" t="n">
-        <v>6.11572647094727</v>
+        <v>6.11572599411011</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>5.99006032943726</v>
+        <v>5.99006080627441</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>5.91559171676636</v>
+        <v>5.91559267044067</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>6.03660440444946</v>
+        <v>6.0366039276123</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.0133318901062</v>
+        <v>6.01333236694336</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.98075246810913</v>
+        <v>5.98075199127197</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G507" t="n">
-        <v>5.94817209243774</v>
+        <v>5.94817304611206</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G509" t="n">
-        <v>6.04125785827637</v>
+        <v>6.04125738143921</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G511" t="n">
-        <v>5.99937009811401</v>
+        <v>5.99936962127686</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>5.91559171676636</v>
+        <v>5.91559267044067</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G514" t="n">
-        <v>5.82716035842896</v>
+        <v>5.82716083526611</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G515" t="n">
-        <v>5.92024660110474</v>
+        <v>5.92024707794189</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G516" t="n">
-        <v>5.88301229476929</v>
+        <v>5.88301277160645</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>5.8597412109375</v>
+        <v>5.85974025726318</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>5.88766622543335</v>
+        <v>5.88766717910767</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G523" t="n">
-        <v>5.96213483810425</v>
+        <v>5.96213579177856</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G524" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.97609853744507</v>
+        <v>5.97609806060791</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>5.85043287277222</v>
+        <v>5.85043239593506</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>5.88766622543335</v>
+        <v>5.88766717910767</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>5.98075246810913</v>
+        <v>5.98075199127197</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351768493652</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G534" t="n">
-        <v>6.06452941894531</v>
+        <v>6.06452894210815</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G535" t="n">
-        <v>6.02264022827148</v>
+        <v>6.02264070510864</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093826293945</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G537" t="n">
-        <v>5.76665592193604</v>
+        <v>5.76665544509888</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734567642212</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>5.58048295974731</v>
+        <v>5.58048439025879</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G540" t="n">
-        <v>5.62702655792236</v>
+        <v>5.62702703475952</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>5.65029811859131</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>5.64098930358887</v>
+        <v>5.64098978042603</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>5.74803781509399</v>
+        <v>5.74803829193115</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>5.68287897109985</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>5.79923486709595</v>
+        <v>5.79923534393311</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G548" t="n">
-        <v>5.83181428909302</v>
+        <v>5.83181524276733</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G550" t="n">
-        <v>5.79923486709595</v>
+        <v>5.79923534393311</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>5.44550895690918</v>
+        <v>5.44550943374634</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>5.34777021408081</v>
+        <v>5.34776973724365</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G561" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G563" t="n">
-        <v>5.65029811859131</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G564" t="n">
-        <v>5.71545839309692</v>
+        <v>5.71545886993408</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>5.64564371109009</v>
+        <v>5.6456446647644</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>5.67822408676147</v>
+        <v>5.67822456359863</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.74803781509399</v>
+        <v>5.74803829193115</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G571" t="n">
-        <v>5.68753290176392</v>
+        <v>5.68753337860107</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>5.74338293075562</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>5.72476625442505</v>
+        <v>5.72476720809937</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.84577894210815</v>
+        <v>5.84577798843384</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G580" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351768493652</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G581" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G582" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.89697504043579</v>
+        <v>5.89697551727295</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G584" t="n">
-        <v>5.92490100860596</v>
+        <v>5.9249005317688</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G586" t="n">
-        <v>5.80854415893555</v>
+        <v>5.80854225158691</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G587" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G589" t="n">
-        <v>5.68753290176392</v>
+        <v>5.68753337860107</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G590" t="n">
-        <v>5.72942066192627</v>
+        <v>5.72942113876343</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734567642212</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>5.78527355194092</v>
+        <v>5.7852725982666</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G596" t="n">
-        <v>5.76665592193604</v>
+        <v>5.76665544509888</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G597" t="n">
-        <v>5.76665592193604</v>
+        <v>5.76665544509888</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>5.77596426010132</v>
+        <v>5.77596378326416</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G600" t="n">
-        <v>5.82716035842896</v>
+        <v>5.82716083526611</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.2350001335144</v>
       </c>
       <c r="G602" t="n">
-        <v>5.80388975143433</v>
+        <v>5.80388927459717</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G603" t="n">
-        <v>5.87835836410522</v>
+        <v>5.87835741043091</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G606" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093826293945</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>5.925048828125</v>
+        <v>5.92504835128784</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G609" t="n">
-        <v>5.9297399520874</v>
+        <v>5.92974042892456</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>5.90159273147583</v>
+        <v>5.90159225463867</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G611" t="n">
-        <v>5.99072599411011</v>
+        <v>5.99072647094727</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>6.09393358230591</v>
+        <v>6.09393310546875</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G618" t="n">
-        <v>6.07047748565674</v>
+        <v>6.07047700881958</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G620" t="n">
-        <v>6.15961122512817</v>
+        <v>6.15961074829102</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G623" t="n">
-        <v>6.19714069366455</v>
+        <v>6.19714117050171</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>6.29096555709839</v>
+        <v>6.29096651077271</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.49738121032715</v>
+        <v>6.49738168716431</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>6.59120607376099</v>
+        <v>6.59120559692383</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G628" t="n">
-        <v>6.59589815139771</v>
+        <v>6.59589767456055</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>6.52083730697632</v>
+        <v>6.52083778381348</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>6.47392559051514</v>
+        <v>6.47392463684082</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>6.40824747085571</v>
+        <v>6.40824699401855</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G632" t="n">
-        <v>6.49738121032715</v>
+        <v>6.49738168716431</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G633" t="n">
-        <v>6.48330736160278</v>
+        <v>6.48330783843994</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G635" t="n">
-        <v>6.55367612838745</v>
+        <v>6.55367660522461</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>6.47392559051514</v>
+        <v>6.47392463684082</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G639" t="n">
-        <v>6.72256183624268</v>
+        <v>6.72256088256836</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.375</v>
       </c>
       <c r="G642" t="n">
-        <v>6.91959381103516</v>
+        <v>6.919593334198</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>6.82107734680176</v>
+        <v>6.82107782363892</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G647" t="n">
-        <v>6.80700397491455</v>
+        <v>6.80700302124023</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G649" t="n">
-        <v>6.94304943084717</v>
+        <v>6.94305038452148</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G650" t="n">
-        <v>6.98996257781982</v>
+        <v>6.98996210098267</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G651" t="n">
-        <v>7.06971311569214</v>
+        <v>7.06971406936646</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G655" t="n">
-        <v>7.16822957992554</v>
+        <v>7.1682300567627</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>7.01810932159424</v>
+        <v>7.01811027526855</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G657" t="n">
-        <v>6.94304943084717</v>
+        <v>6.94305038452148</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>6.84453439712524</v>
+        <v>6.84453392028809</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>6.7647819519043</v>
+        <v>6.76478242874146</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>6.89613676071167</v>
+        <v>6.89613723754883</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G664" t="n">
-        <v>6.87268161773682</v>
+        <v>6.87268114089966</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G665" t="n">
-        <v>6.88675451278687</v>
+        <v>6.88675498962402</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>6.80700397491455</v>
+        <v>6.80700302124023</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>6.97119808197021</v>
+        <v>6.9711971282959</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G671" t="n">
-        <v>7.10255289077759</v>
+        <v>7.10255193710327</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>7.30427598953247</v>
+        <v>7.30427551269531</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G673" t="n">
-        <v>7.1869945526123</v>
+        <v>7.18699502944946</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>7.625</v>
       </c>
       <c r="G674" t="n">
-        <v>7.15415620803833</v>
+        <v>7.15415573120117</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>7.13539123535156</v>
+        <v>7.1353907585144</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G678" t="n">
-        <v>7.0744047164917</v>
+        <v>7.07440567016602</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>7.13539123535156</v>
+        <v>7.1353907585144</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G680" t="n">
-        <v>7.14477252960205</v>
+        <v>7.14477348327637</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>7.625</v>
       </c>
       <c r="G681" t="n">
-        <v>7.15415620803833</v>
+        <v>7.15415573120117</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>7.01810932159424</v>
+        <v>7.01811027526855</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>6.95243215560913</v>
+        <v>6.95243263244629</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156637191772</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>7.06033134460449</v>
+        <v>7.06033182144165</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>7.13539123535156</v>
+        <v>7.1353907585144</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G690" t="n">
-        <v>6.80700397491455</v>
+        <v>6.80700302124023</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>6.89613676071167</v>
+        <v>6.89613723754883</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G693" t="n">
-        <v>6.89613676071167</v>
+        <v>6.89613723754883</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G695" t="n">
-        <v>6.80700397491455</v>
+        <v>6.80700302124023</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>6.83984279632568</v>
+        <v>6.83984231948853</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>7.375</v>
       </c>
       <c r="G699" t="n">
-        <v>6.91959381103516</v>
+        <v>6.919593334198</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>6.96181488037109</v>
+        <v>6.96181535720825</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G701" t="n">
-        <v>6.88206386566162</v>
+        <v>6.88206338882446</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G702" t="n">
-        <v>7.0228009223938</v>
+        <v>7.02280139923096</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>6.94304943084717</v>
+        <v>6.94305038452148</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G704" t="n">
-        <v>6.94304943084717</v>
+        <v>6.94305038452148</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G705" t="n">
-        <v>6.7741641998291</v>
+        <v>6.77416467666626</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>6.60527944564819</v>
+        <v>6.60527992248535</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G707" t="n">
-        <v>6.53960275650024</v>
+        <v>6.53960227966309</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>6.55836725234985</v>
+        <v>6.55836772918701</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>6.23467111587524</v>
+        <v>6.2346715927124</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>6.10331630706787</v>
+        <v>6.10331583023071</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G713" t="n">
-        <v>6.12208080291748</v>
+        <v>6.12208127975464</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>6.22059726715088</v>
+        <v>6.2205982208252</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G716" t="n">
-        <v>6.23936223983765</v>
+        <v>6.2393627166748</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>6.03294706344604</v>
+        <v>6.0329475402832</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>6.06109428405762</v>
+        <v>6.06109523773193</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>6.29096555709839</v>
+        <v>6.29096651077271</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>6.37540912628174</v>
+        <v>6.37540817260742</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>6.37071704864502</v>
+        <v>6.37071752548218</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.75</v>
       </c>
       <c r="G726" t="n">
-        <v>6.33318758010864</v>
+        <v>6.3331880569458</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G728" t="n">
-        <v>6.66626691818237</v>
+        <v>6.66626644134521</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>6.88206386566162</v>
+        <v>6.88206338882446</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G731" t="n">
-        <v>6.97588872909546</v>
+        <v>6.9758882522583</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>7.00403594970703</v>
+        <v>7.00403642654419</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>7.1869945526123</v>
+        <v>7.18699502944946</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G734" t="n">
-        <v>7.01341772079468</v>
+        <v>7.01341819763184</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G735" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156637191772</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>7.21514225006104</v>
+        <v>7.21514272689819</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G739" t="n">
-        <v>6.92897605895996</v>
+        <v>6.92897653579712</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>6.89613676071167</v>
+        <v>6.89613723754883</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G741" t="n">
-        <v>7.04625844955444</v>
+        <v>7.04625701904297</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G742" t="n">
-        <v>6.98996257781982</v>
+        <v>6.98996210098267</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G743" t="n">
-        <v>6.93835830688477</v>
+        <v>6.93835878372192</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>6.89613676071167</v>
+        <v>6.89613723754883</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>6.92428493499756</v>
+        <v>6.92428541183472</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G747" t="n">
-        <v>6.94304943084717</v>
+        <v>6.94305038452148</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>7.00403594970703</v>
+        <v>7.00403642654419</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G749" t="n">
-        <v>7.06502294540405</v>
+        <v>7.06502246856689</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>7.25267267227173</v>
+        <v>7.25267219543457</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>7.06502294540405</v>
+        <v>7.06502246856689</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>7.5</v>
       </c>
       <c r="G753" t="n">
-        <v>7.03687524795532</v>
+        <v>7.03687477111816</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21514225006104</v>
+        <v>7.21514272689819</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G756" t="n">
-        <v>7.21045160293579</v>
+        <v>7.21045112609863</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>7.21045160293579</v>
+        <v>7.21045112609863</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G760" t="n">
-        <v>7.16822957992554</v>
+        <v>7.1682300567627</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G761" t="n">
-        <v>7.00403594970703</v>
+        <v>7.00403642654419</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G763" t="n">
-        <v>6.92897605895996</v>
+        <v>6.92897653579712</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G765" t="n">
-        <v>7.06502294540405</v>
+        <v>7.06502246856689</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G766" t="n">
-        <v>7.3371148109436</v>
+        <v>7.33711528778076</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>7.75</v>
       </c>
       <c r="G767" t="n">
-        <v>7.2714376449585</v>
+        <v>7.27143716812134</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>7.2198338508606</v>
+        <v>7.21983337402344</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156637191772</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>7.10724306106567</v>
+        <v>7.10724353790283</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>7.75</v>
       </c>
       <c r="G771" t="n">
-        <v>7.2714376449585</v>
+        <v>7.27143716812134</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>7.24328947067261</v>
+        <v>7.24328994750977</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G774" t="n">
-        <v>7.14477252960205</v>
+        <v>7.14477348327637</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G775" t="n">
-        <v>7.44032192230225</v>
+        <v>7.4403223991394</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G777" t="n">
-        <v>7.44032192230225</v>
+        <v>7.4403223991394</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>7.35118865966797</v>
+        <v>7.35118913650513</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G779" t="n">
-        <v>7.3793363571167</v>
+        <v>7.37933540344238</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>7.30896759033203</v>
+        <v>7.30896663665771</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G782" t="n">
-        <v>7.3371148109436</v>
+        <v>7.33711528778076</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>7.51069116592407</v>
+        <v>7.51069164276123</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>7.41686677932739</v>
+        <v>7.41686630249023</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>7.35118865966797</v>
+        <v>7.35118913650513</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G791" t="n">
-        <v>7.40279293060303</v>
+        <v>7.40279340744019</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G792" t="n">
-        <v>7.49661731719971</v>
+        <v>7.49661636352539</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G794" t="n">
-        <v>7.52945613861084</v>
+        <v>7.52945566177368</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G795" t="n">
-        <v>7.61859035491943</v>
+        <v>7.61858987808228</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>7.68895816802979</v>
+        <v>7.6889591217041</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G797" t="n">
-        <v>7.74994611740112</v>
+        <v>7.74994516372681</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>8.25</v>
       </c>
       <c r="G798" t="n">
-        <v>7.74056243896484</v>
+        <v>7.740562915802</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G799" t="n">
-        <v>7.76871061325073</v>
+        <v>7.7687087059021</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G800" t="n">
-        <v>7.80623960494995</v>
+        <v>7.80623912811279</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G801" t="n">
-        <v>7.76871061325073</v>
+        <v>7.7687087059021</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>7.76871061325073</v>
+        <v>7.7687087059021</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G803" t="n">
-        <v>7.834388256073</v>
+        <v>7.83438730239868</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G804" t="n">
-        <v>7.71710729598999</v>
+        <v>7.71710586547852</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G805" t="n">
-        <v>7.86722660064697</v>
+        <v>7.86722612380981</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>7.94228553771973</v>
+        <v>7.9422869682312</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G808" t="n">
-        <v>7.42155694961548</v>
+        <v>7.42155742645264</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>7.40748310089111</v>
+        <v>7.40748357772827</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>8</v>
       </c>
       <c r="G811" t="n">
-        <v>7.50599956512451</v>
+        <v>7.50600004196167</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>7.66081094741821</v>
+        <v>7.66081142425537</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G814" t="n">
-        <v>7.65142869949341</v>
+        <v>7.65142822265625</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>7.914137840271</v>
+        <v>7.91413879394531</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G817" t="n">
-        <v>7.88599252700806</v>
+        <v>7.88599014282227</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G818" t="n">
-        <v>7.92352104187012</v>
+        <v>7.92352151870728</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G819" t="n">
-        <v>7.94697713851929</v>
+        <v>7.94697761535645</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G821" t="n">
-        <v>7.94697713851929</v>
+        <v>7.94697761535645</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G822" t="n">
-        <v>8.20030307769775</v>
+        <v>8.20030403137207</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G823" t="n">
-        <v>8.31758689880371</v>
+        <v>8.31758594512939</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G825" t="n">
-        <v>8.25660037994385</v>
+        <v>8.25660133361816</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>8.75</v>
       </c>
       <c r="G826" t="n">
-        <v>8.20968723297119</v>
+        <v>8.20968818664551</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G829" t="n">
-        <v>8.11117172241211</v>
+        <v>8.11117267608643</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>8.1346263885498</v>
+        <v>8.13462734222412</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G831" t="n">
-        <v>8.13931846618652</v>
+        <v>8.13932037353516</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>8.20030307769775</v>
+        <v>8.20030403137207</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>8.04549312591553</v>
+        <v>8.04549217224121</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G835" t="n">
-        <v>8.24252605438232</v>
+        <v>8.24252700805664</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G836" t="n">
-        <v>8.22845363616943</v>
+        <v>8.2284517288208</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>8.25190830230713</v>
+        <v>8.25190925598145</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G838" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277408599854</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>8.09709739685059</v>
+        <v>8.0970983505249</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>8.38493251800537</v>
+        <v>8.38493156433105</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>8.98499965667725</v>
       </c>
       <c r="G846" t="n">
-        <v>8.47930145263672</v>
+        <v>8.47930335998535</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G847" t="n">
-        <v>8.31415271759033</v>
+        <v>8.31415176391602</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>8.37077522277832</v>
+        <v>8.370774269104</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G849" t="n">
-        <v>8.35661888122559</v>
+        <v>8.3566198348999</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>8.68220138549805</v>
+        <v>8.68220329284668</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.125</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61142253875732</v>
+        <v>8.61142349243164</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G853" t="n">
-        <v>8.70107746124268</v>
+        <v>8.70107841491699</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G854" t="n">
-        <v>8.64445400238037</v>
+        <v>8.64445304870605</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G856" t="n">
-        <v>8.55480003356934</v>
+        <v>8.55479907989502</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>8.57367515563965</v>
+        <v>8.57367420196533</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>8.64917278289795</v>
+        <v>8.64917182922363</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.125</v>
       </c>
       <c r="G859" t="n">
-        <v>8.61142253875732</v>
+        <v>8.61142349243164</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G860" t="n">
-        <v>8.67748355865479</v>
+        <v>8.67748260498047</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G861" t="n">
-        <v>8.63973617553711</v>
+        <v>8.63973522186279</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>8.57367515563965</v>
+        <v>8.57367420196533</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>8.57367515563965</v>
+        <v>8.57367420196533</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G866" t="n">
-        <v>8.40852355957031</v>
+        <v>8.40852451324463</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G869" t="n">
-        <v>8.24809074401855</v>
+        <v>8.24809169769287</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G870" t="n">
-        <v>8.28112125396729</v>
+        <v>8.2811222076416</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G871" t="n">
-        <v>8.31415271759033</v>
+        <v>8.31415176391602</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G873" t="n">
-        <v>8.2858419418335</v>
+        <v>8.28584098815918</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G874" t="n">
-        <v>8.20090579986572</v>
+        <v>8.20090675354004</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G875" t="n">
-        <v>8.31415271759033</v>
+        <v>8.31415176391602</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G876" t="n">
-        <v>8.32830715179443</v>
+        <v>8.32830810546875</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G877" t="n">
-        <v>8.29055881500244</v>
+        <v>8.29056072235107</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G878" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696586608887</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G879" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>8.4179630279541</v>
+        <v>8.41796207427979</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>8.68220138549805</v>
+        <v>8.68220329284668</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>8.09709739685059</v>
+        <v>8.0970983505249</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G889" t="n">
-        <v>8.22921848297119</v>
+        <v>8.22921752929688</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G892" t="n">
-        <v>8.35661888122559</v>
+        <v>8.3566198348999</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G893" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G894" t="n">
-        <v>8.32830715179443</v>
+        <v>8.32830810546875</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>8.29527759552002</v>
+        <v>8.2952766418457</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G896" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696586608887</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G897" t="n">
-        <v>8.24337291717529</v>
+        <v>8.24337387084961</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G898" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G899" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>8.09709739685059</v>
+        <v>8.0970983505249</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G902" t="n">
-        <v>8.15843868255615</v>
+        <v>8.15843963623047</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G905" t="n">
-        <v>8.04047679901123</v>
+        <v>8.04047584533691</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12540817260742</v>
+        <v>8.12540912628174</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G908" t="n">
-        <v>8.04991149902344</v>
+        <v>8.04991054534912</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>7.97441387176514</v>
+        <v>7.97441339492798</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>8.02631950378418</v>
+        <v>8.02631855010986</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.94610214233398</v>
+        <v>7.94610261917114</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G912" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779041290283</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G913" t="n">
-        <v>7.85172986984253</v>
+        <v>7.85173034667969</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>7.50727367401123</v>
+        <v>7.50727415084839</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G917" t="n">
-        <v>7.54502201080322</v>
+        <v>7.54502248764038</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>7.38930892944336</v>
+        <v>7.38930988311768</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G919" t="n">
-        <v>7.60636425018311</v>
+        <v>7.60636472702026</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G920" t="n">
-        <v>7.47896194458008</v>
+        <v>7.47896289825439</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>7.34684228897095</v>
+        <v>7.34684133529663</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G923" t="n">
-        <v>7.54030418395996</v>
+        <v>7.54030323028564</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G924" t="n">
-        <v>7.48368072509766</v>
+        <v>7.48368120193481</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G925" t="n">
-        <v>7.79039001464844</v>
+        <v>7.79038906097412</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>7.83285570144653</v>
+        <v>7.83285665512085</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G927" t="n">
-        <v>7.70545387268066</v>
+        <v>7.70545482635498</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G928" t="n">
-        <v>7.76207876205444</v>
+        <v>7.76207733154297</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>7.98385047912598</v>
+        <v>7.98385095596313</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G930" t="n">
-        <v>7.97441387176514</v>
+        <v>7.97441339492798</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G931" t="n">
-        <v>8.08294105529785</v>
+        <v>8.08294200897217</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.15843868255615</v>
+        <v>8.15843963623047</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>7.99800729751587</v>
+        <v>7.99800682067871</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G939" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779041290283</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G940" t="n">
-        <v>7.91307353973389</v>
+        <v>7.91307258605957</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G943" t="n">
-        <v>7.69129848480225</v>
+        <v>7.6912989616394</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>7.79510831832886</v>
+        <v>7.7951078414917</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G945" t="n">
-        <v>7.76679658889771</v>
+        <v>7.76679611206055</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G946" t="n">
-        <v>7.71017360687256</v>
+        <v>7.71017265319824</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G947" t="n">
-        <v>7.7290472984314</v>
+        <v>7.72904777526855</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G948" t="n">
-        <v>7.76679658889771</v>
+        <v>7.76679611206055</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G949" t="n">
-        <v>7.88004350662231</v>
+        <v>7.880042552948</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G950" t="n">
-        <v>7.78095245361328</v>
+        <v>7.78095149993896</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G951" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779041290283</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>8.25</v>
       </c>
       <c r="G952" t="n">
-        <v>7.78567028045654</v>
+        <v>7.78567123413086</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>7.82341861724854</v>
+        <v>7.82341957092285</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G954" t="n">
-        <v>7.83285570144653</v>
+        <v>7.83285665512085</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G955" t="n">
-        <v>7.60164642333984</v>
+        <v>7.60164594650269</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G957" t="n">
-        <v>7.88004350662231</v>
+        <v>7.880042552948</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G959" t="n">
-        <v>7.91307353973389</v>
+        <v>7.91307258605957</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G960" t="n">
-        <v>7.97441387176514</v>
+        <v>7.97441339492798</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G961" t="n">
-        <v>7.99328851699829</v>
+        <v>7.99328899383545</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G962" t="n">
-        <v>8.00744533538818</v>
+        <v>8.00744438171387</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G964" t="n">
-        <v>8.00744533538818</v>
+        <v>8.00744438171387</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G966" t="n">
-        <v>7.81398248672485</v>
+        <v>7.81398105621338</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>7.63467645645142</v>
+        <v>7.63467597961426</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>7.60636425018311</v>
+        <v>7.60636472702026</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G969" t="n">
-        <v>7.46480703353882</v>
+        <v>7.46480655670166</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>7.52614879608154</v>
+        <v>7.52614831924438</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G974" t="n">
-        <v>7.81398248672485</v>
+        <v>7.81398105621338</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G975" t="n">
-        <v>7.69601774215698</v>
+        <v>7.69601678848267</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G976" t="n">
-        <v>7.75264072418213</v>
+        <v>7.75263977050781</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G978" t="n">
-        <v>7.81398248672485</v>
+        <v>7.81398105621338</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>7.83285570144653</v>
+        <v>7.83285665512085</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>7.77623319625854</v>
+        <v>7.7762336730957</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G985" t="n">
-        <v>7.73376607894897</v>
+        <v>7.73376655578613</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>7.86588621139526</v>
+        <v>7.86588668823242</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>7.86588621139526</v>
+        <v>7.86588668823242</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G989" t="n">
-        <v>7.79510831832886</v>
+        <v>7.7951078414917</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>7.83285570144653</v>
+        <v>7.83285665512085</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G991" t="n">
-        <v>7.84701108932495</v>
+        <v>7.84701299667358</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>7.80926275253296</v>
+        <v>7.80926370620728</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G993" t="n">
-        <v>7.84701108932495</v>
+        <v>7.84701299667358</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>7.98385047912598</v>
+        <v>7.98385095596313</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>7.98856973648071</v>
+        <v>7.98857069015503</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G996" t="n">
-        <v>7.92722749710083</v>
+        <v>7.92722845077515</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>7.81869983673096</v>
+        <v>7.81870126724243</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G998" t="n">
-        <v>7.66298818588257</v>
+        <v>7.66298723220825</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>7.7007360458374</v>
+        <v>7.70073652267456</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>7.71017360687256</v>
+        <v>7.71017265319824</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>7.71017360687256</v>
+        <v>7.71017265319824</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1002" t="n">
-        <v>7.73376607894897</v>
+        <v>7.73376655578613</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>7.70545387268066</v>
+        <v>7.70545482635498</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G1004" t="n">
-        <v>7.72432947158813</v>
+        <v>7.72432899475098</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G1005" t="n">
-        <v>7.76207876205444</v>
+        <v>7.76207733154297</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1007" t="n">
-        <v>7.60636425018311</v>
+        <v>7.60636472702026</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1010" t="n">
-        <v>7.73376607894897</v>
+        <v>7.73376655578613</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1011" t="n">
-        <v>7.68186140060425</v>
+        <v>7.68186187744141</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>7.79039001464844</v>
+        <v>7.79038906097412</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G1014" t="n">
-        <v>7.79982614517212</v>
+        <v>7.79982709884644</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1015" t="n">
-        <v>7.68186140060425</v>
+        <v>7.68186187744141</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>7.66298818588257</v>
+        <v>7.66298723220825</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1018" t="n">
-        <v>7.69129848480225</v>
+        <v>7.6912989616394</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1019" t="n">
-        <v>7.59692764282227</v>
+        <v>7.59692716598511</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G1021" t="n">
-        <v>7.76207876205444</v>
+        <v>7.76207733154297</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>7.74320411682129</v>
+        <v>7.74320363998413</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1026" t="n">
-        <v>7.9555401802063</v>
+        <v>7.95554065704346</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.12540817260742</v>
+        <v>8.12540912628174</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.09237861633301</v>
+        <v>8.09237766265869</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.14428329467773</v>
+        <v>8.14428424835205</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.22921848297119</v>
+        <v>8.22921752929688</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.21034336090088</v>
+        <v>8.21034240722656</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696586608887</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.38493251800537</v>
+        <v>8.38493156433105</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.32358837127686</v>
+        <v>8.32358932495117</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.23865604400635</v>
+        <v>8.23865509033203</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.42267990112305</v>
+        <v>8.42268085479736</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.55480003356934</v>
+        <v>8.55479907989502</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.55951881408691</v>
+        <v>8.55951976776123</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.45570945739746</v>
+        <v>8.45571041107178</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.40852355957031</v>
+        <v>8.40852451324463</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>8.98499965667725</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.47930145263672</v>
+        <v>8.47930335998535</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.04047679901123</v>
+        <v>8.04047584533691</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.06878566741943</v>
+        <v>8.06878662109375</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.62523889541626</v>
+        <v>7.6252384185791</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.58749055862427</v>
+        <v>7.58749008178711</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>8.125</v>
       </c>
       <c r="G1055" t="n">
-        <v>7.66770601272583</v>
+        <v>7.66770553588867</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.11563062667847</v>
+        <v>7.11563158035278</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.19112825393677</v>
+        <v>7.19112873077393</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.22887706756592</v>
+        <v>7.22887754440308</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.59658622741699</v>
+        <v>6.59658670425415</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.59658622741699</v>
+        <v>6.59658670425415</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.94542074203491</v>
+        <v>5.94542121887207</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.20494318008423</v>
+        <v>6.20494270324707</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.66736555099487</v>
+        <v>6.66736507415771</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>6.18135118484497</v>
+        <v>6.18135023117065</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.37799978256226</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.0190315246582</v>
+        <v>6.01903104782104</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.7680025100708</v>
+        <v>5.76800203323364</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.28515958786011</v>
+        <v>6.28515911102295</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.25684785842896</v>
+        <v>6.25684881210327</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.68800020217896</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.31158351898193</v>
+        <v>6.31158399581909</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6.75600004196167</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.37575626373291</v>
+        <v>6.37575674057007</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.55883741378784</v>
+        <v>6.558837890625</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.40188121795654</v>
+        <v>6.40188217163086</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.33339214324951</v>
+        <v>6.33339262008667</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>6.29724550247192</v>
+        <v>6.29724502563477</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G1095" t="n">
-        <v>6.34670972824097</v>
+        <v>6.34671020507812</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.4970064163208</v>
+        <v>6.49700689315796</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>6.51603126525879</v>
+        <v>6.51603174209595</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>7.03399991989136</v>
       </c>
       <c r="G1098" t="n">
-        <v>6.6910605430603</v>
+        <v>6.69106101989746</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.72530555725098</v>
+        <v>6.72530603408813</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.52364158630371</v>
+        <v>6.52364110946655</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.00600004196167</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.66442584991455</v>
+        <v>6.66442632675171</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.83374786376953</v>
+        <v>6.83374738693237</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>6.90399980545044</v>
       </c>
       <c r="G1109" t="n">
-        <v>6.56739854812622</v>
+        <v>6.5673975944519</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>6.74200010299683</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.41329717636108</v>
+        <v>6.41329669952393</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>6.57310628890991</v>
+        <v>6.57310581207275</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.56359386444092</v>
+        <v>6.56359434127808</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>6.91400003433228</v>
       </c>
       <c r="G1115" t="n">
-        <v>6.57691097259521</v>
+        <v>6.57691144943237</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.96799993515015</v>
       </c>
       <c r="G1116" t="n">
-        <v>6.62827920913696</v>
+        <v>6.6282787322998</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1117" t="n">
-        <v>6.61115646362305</v>
+        <v>6.61115694046021</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.0392165184021</v>
+        <v>7.03921699523926</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1119" t="n">
-        <v>6.94409275054932</v>
+        <v>6.94409227371216</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>6.83945512771606</v>
+        <v>6.83945560455322</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.0392165184021</v>
+        <v>7.03921699523926</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.0354118347168</v>
+        <v>7.03541088104248</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>7.43200016021729</v>
       </c>
       <c r="G1127" t="n">
-        <v>7.06965684890747</v>
+        <v>7.06965637207031</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>6.95360422134399</v>
+        <v>6.95360469818115</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.09629154205322</v>
+        <v>7.09629106521606</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>7.57200002670288</v>
       </c>
       <c r="G1131" t="n">
-        <v>7.20283031463623</v>
+        <v>7.20283126831055</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>7.2199535369873</v>
+        <v>7.21995306015015</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G1134" t="n">
-        <v>7.33600473403931</v>
+        <v>7.33600521087646</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>7.7039999961853</v>
       </c>
       <c r="G1135" t="n">
-        <v>7.3283953666687</v>
+        <v>7.32839584350586</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.0392165184021</v>
+        <v>7.03921699523926</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>7.52600002288818</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.15907335281372</v>
+        <v>7.15907382965088</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.2332706451416</v>
+        <v>7.23327112197876</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>7.89699983596802</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.51198530197144</v>
+        <v>7.51198577880859</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>7.94199991226196</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.55479097366333</v>
+        <v>7.55479145050049</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.59093904495239</v>
+        <v>7.59093952178955</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.72411394119263</v>
+        <v>7.72411346435547</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>8.14299964904785</v>
       </c>
       <c r="G1149" t="n">
-        <v>7.74599123001099</v>
+        <v>7.7459921836853</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>8.09200000762939</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.69747829437256</v>
+        <v>7.6974778175354</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.63374423980713</v>
+        <v>7.63374376296997</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.80497026443481</v>
+        <v>7.80496978759766</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>8.10599994659424</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.71079587936401</v>
+        <v>7.71079683303833</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>8.26799964904785</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.86489677429199</v>
+        <v>7.86489772796631</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>8.15200042724609</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.75455379486084</v>
+        <v>7.75455331802368</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>7.76691913604736</v>
+        <v>7.76691865921021</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.72030782699585</v>
+        <v>7.72030830383301</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.72599983215332</v>
       </c>
       <c r="G1162" t="n">
-        <v>8.30056762695312</v>
+        <v>8.30056667327881</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>8.51299953460693</v>
       </c>
       <c r="G1164" t="n">
-        <v>8.09795188903809</v>
+        <v>8.09795093536377</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.15692901611328</v>
+        <v>8.1569299697876</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.1084156036377</v>
+        <v>8.10841655731201</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.3091287612915</v>
+        <v>8.30912780761719</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.15692901611328</v>
+        <v>8.1569299697876</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>8.63899993896484</v>
       </c>
       <c r="G1181" t="n">
-        <v>8.21781063079834</v>
+        <v>8.21780872344971</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G1183" t="n">
-        <v>8.18546676635742</v>
+        <v>8.18546772003174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>8.4709997177124</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.05800151824951</v>
+        <v>8.0580005645752</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>8.59200000762939</v>
       </c>
       <c r="G1185" t="n">
-        <v>8.17310237884521</v>
+        <v>8.1731014251709</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G1186" t="n">
-        <v>8.35574150085449</v>
+        <v>8.35574054718018</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9.02700042724609</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.58689403533936</v>
+        <v>8.58689308166504</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9.06599998474121</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.62399196624756</v>
+        <v>8.62399291992188</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1196" t="n">
-        <v>8.81328868865967</v>
+        <v>8.8132905960083</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.87892532348633</v>
+        <v>8.87892436981201</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>9.38199996948242</v>
       </c>
       <c r="G1199" t="n">
-        <v>8.92458534240723</v>
+        <v>8.92458438873291</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>9.16699981689453</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.72006702423096</v>
+        <v>8.72006797790527</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.80567932128906</v>
+        <v>8.80567836761475</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.88082885742188</v>
+        <v>8.88082790374756</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>9.41100025177002</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.95217132568359</v>
+        <v>8.95217037200928</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G1209" t="n">
-        <v>8.91031742095947</v>
+        <v>8.91031646728516</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>9.34899997711182</v>
       </c>
       <c r="G1210" t="n">
-        <v>8.89319324493408</v>
+        <v>8.8931941986084</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>9.27200031280518</v>
       </c>
       <c r="G1211" t="n">
-        <v>8.81994724273682</v>
+        <v>8.81994819641113</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>8.86085224151611</v>
+        <v>8.8608512878418</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1213" t="n">
-        <v>8.83707141876221</v>
+        <v>8.83707046508789</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>9.07488250732422</v>
+        <v>9.0748815536499</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>9.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>9.03683090209961</v>
+        <v>9.03683185577393</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G1218" t="n">
-        <v>8.92553615570068</v>
+        <v>8.925537109375</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>9.11200046539307</v>
       </c>
       <c r="G1222" t="n">
-        <v>8.66774940490723</v>
+        <v>8.66774845123291</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G1223" t="n">
-        <v>8.80092430114746</v>
+        <v>8.80092334747314</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>9.26399993896484</v>
       </c>
       <c r="G1224" t="n">
-        <v>8.81233978271484</v>
+        <v>8.81233882904053</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>8.60877227783203</v>
+        <v>8.6087703704834</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G1226" t="n">
-        <v>8.75526428222656</v>
+        <v>8.75526332855225</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1227" t="n">
-        <v>8.53267192840576</v>
+        <v>8.53267288208008</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G1228" t="n">
-        <v>8.37476634979248</v>
+        <v>8.37476539611816</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>8.90200042724609</v>
       </c>
       <c r="G1231" t="n">
-        <v>8.46798706054688</v>
+        <v>8.46798610687256</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>9.20600032806396</v>
       </c>
       <c r="G1233" t="n">
-        <v>8.75716686248779</v>
+        <v>8.75716590881348</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>9.62800025939941</v>
       </c>
       <c r="G1239" t="n">
-        <v>9.15859127044678</v>
+        <v>9.15859222412109</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>9.57800006866455</v>
       </c>
       <c r="G1243" t="n">
-        <v>9.11102867126465</v>
+        <v>9.11102962493896</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>9.45600032806396</v>
       </c>
       <c r="G1244" t="n">
-        <v>8.99497890472412</v>
+        <v>8.9949779510498</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1246" t="n">
-        <v>8.93219661712646</v>
+        <v>8.93219566345215</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1247" t="n">
-        <v>9.05585765838623</v>
+        <v>9.05585670471191</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G1253" t="n">
-        <v>8.99307632446289</v>
+        <v>8.99307537078857</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>9.48400020599365</v>
       </c>
       <c r="G1254" t="n">
-        <v>9.02161121368408</v>
+        <v>9.02161312103271</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>9.5</v>
       </c>
       <c r="G1255" t="n">
-        <v>9.03683090209961</v>
+        <v>9.03683185577393</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G1257" t="n">
-        <v>8.86941337585449</v>
+        <v>8.86941242218018</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1259" t="n">
-        <v>8.92268371582031</v>
+        <v>8.922682762146</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.81804656982422</v>
+        <v>8.8180456161499</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>9.25599956512451</v>
       </c>
       <c r="G1264" t="n">
-        <v>8.80472850799561</v>
+        <v>8.80472755432129</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>8.73623847961426</v>
+        <v>8.73623752593994</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G1266" t="n">
-        <v>8.75526428222656</v>
+        <v>8.75526332855225</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>9.28400039672852</v>
       </c>
       <c r="G1268" t="n">
-        <v>8.8313627243042</v>
+        <v>8.83136367797852</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>9.46199989318848</v>
       </c>
       <c r="G1269" t="n">
-        <v>9.00068473815918</v>
+        <v>9.00068378448486</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1270" t="n">
-        <v>8.88463401794434</v>
+        <v>8.88463306427002</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.77048301696777</v>
+        <v>8.77048397064209</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>8.97200012207031</v>
       </c>
       <c r="G1272" t="n">
-        <v>8.53457355499268</v>
+        <v>8.53457546234131</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>8.89799976348877</v>
       </c>
       <c r="G1273" t="n">
-        <v>8.4641809463501</v>
+        <v>8.46418190002441</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G1274" t="n">
-        <v>8.41281509399414</v>
+        <v>8.41281414031982</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1276" t="n">
-        <v>8.29486179351807</v>
+        <v>8.29486083984375</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>8.67800045013428</v>
       </c>
       <c r="G1277" t="n">
-        <v>8.25490856170654</v>
+        <v>8.25490951538086</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G1278" t="n">
-        <v>8.34622955322266</v>
+        <v>8.34622859954834</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>8.72200012207031</v>
       </c>
       <c r="G1279" t="n">
-        <v>8.29676342010498</v>
+        <v>8.2967643737793</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>8.79399967193604</v>
       </c>
       <c r="G1282" t="n">
-        <v>8.36525249481201</v>
+        <v>8.36525344848633</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G1283" t="n">
-        <v>8.35574150085449</v>
+        <v>8.35574054718018</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>8.81400012969971</v>
       </c>
       <c r="G1285" t="n">
-        <v>8.38427639007568</v>
+        <v>8.38427734375</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1288" t="n">
-        <v>8.46608352661133</v>
+        <v>8.46608448028564</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G1290" t="n">
-        <v>8.4432544708252</v>
+        <v>8.44325542449951</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>8.88199996948242</v>
       </c>
       <c r="G1291" t="n">
-        <v>8.44896221160889</v>
+        <v>8.44896125793457</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1292" t="n">
-        <v>8.69438362121582</v>
+        <v>8.69438457489014</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>9.18200016021729</v>
       </c>
       <c r="G1293" t="n">
-        <v>8.73433589935303</v>
+        <v>8.73433685302734</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G1294" t="n">
-        <v>8.80663108825684</v>
+        <v>8.80663204193115</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>9.73600006103516</v>
       </c>
       <c r="G1297" t="n">
-        <v>9.26132583618164</v>
+        <v>9.26132678985596</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G1299" t="n">
-        <v>9.2442045211792</v>
+        <v>9.24420261383057</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>9.21186065673828</v>
+        <v>9.2118616104126</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G1306" t="n">
-        <v>9.0672721862793</v>
+        <v>9.06727123260498</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>9.61800003051758</v>
       </c>
       <c r="G1307" t="n">
-        <v>9.14907836914062</v>
+        <v>9.14907932281494</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G1308" t="n">
-        <v>9.17571353912354</v>
+        <v>9.17571258544922</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G1309" t="n">
-        <v>9.2004451751709</v>
+        <v>9.20044612884521</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G1311" t="n">
-        <v>9.053955078125</v>
+        <v>9.05395412445068</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1312" t="n">
-        <v>9.02541732788086</v>
+        <v>9.02541637420654</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1313" t="n">
-        <v>8.91316986083984</v>
+        <v>8.91317081451416</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>9.49400043487549</v>
       </c>
       <c r="G1315" t="n">
-        <v>9.03112411499023</v>
+        <v>9.03112506866455</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1316" t="n">
-        <v>9.22708225250244</v>
+        <v>9.22708129882812</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>9.86200046539307</v>
       </c>
       <c r="G1317" t="n">
-        <v>9.38118457794189</v>
+        <v>9.38118362426758</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1318" t="n">
-        <v>9.61709022521973</v>
+        <v>9.61709117889404</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1321" t="n">
-        <v>9.24610710144043</v>
+        <v>9.24610614776611</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1323" t="n">
-        <v>9.28415584564209</v>
+        <v>9.28415489196777</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G1324" t="n">
-        <v>9.22327518463135</v>
+        <v>9.22327613830566</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1327" t="n">
-        <v>9.10341835021973</v>
+        <v>9.10341930389404</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>9.48400020599365</v>
       </c>
       <c r="G1328" t="n">
-        <v>9.02161121368408</v>
+        <v>9.02161312103271</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>9.59200000762939</v>
       </c>
       <c r="G1329" t="n">
-        <v>9.12434768676758</v>
+        <v>9.12434577941895</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>9.61600017547607</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.14717769622803</v>
+        <v>9.14717674255371</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>9.75</v>
       </c>
       <c r="G1338" t="n">
-        <v>9.27464294433594</v>
+        <v>9.27464389801025</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.49342918395996</v>
+        <v>9.49343013763428</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.42113494873047</v>
+        <v>9.42113590240479</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>9.98600006103516</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.49913787841797</v>
+        <v>9.49913597106934</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>9.83800029754639</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.41018295288086</v>
+        <v>9.41018199920654</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>9.91600036621094</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.48478984832764</v>
+        <v>9.48479080200195</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>9.48861598968506</v>
+        <v>9.48861503601074</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.7325267791748</v>
+        <v>9.73252773284912</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.79470062255859</v>
+        <v>9.79469966888428</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>10.1049995422363</v>
       </c>
       <c r="G1363" t="n">
-        <v>9.66557121276855</v>
+        <v>9.66557025909424</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.67991924285889</v>
+        <v>9.67991828918457</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>10.085000038147</v>
       </c>
       <c r="G1366" t="n">
-        <v>9.64643955230713</v>
+        <v>9.64644050598145</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.0146989822388</v>
+        <v>10.0146980285645</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.1246967315674</v>
+        <v>10.1246976852417</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.1581745147705</v>
+        <v>10.1581735610962</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1377" t="n">
-        <v>10.1581745147705</v>
+        <v>10.1581735610962</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.2346963882446</v>
+        <v>10.2346973419189</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.4164333343506</v>
+        <v>10.4164342880249</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1380" t="n">
-        <v>10.4738245010376</v>
+        <v>10.4738254547119</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G1381" t="n">
-        <v>10.6507797241211</v>
+        <v>10.6507806777954</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1382" t="n">
-        <v>10.6555614471436</v>
+        <v>10.6555624008179</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1384" t="n">
-        <v>10.660346031189</v>
+        <v>10.6603450775146</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1385" t="n">
-        <v>10.660346031189</v>
+        <v>10.6603450775146</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>11.1049995422363</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.6220836639404</v>
+        <v>10.6220827102661</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1394" t="n">
-        <v>10.8946905136108</v>
+        <v>10.8946914672852</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>11.375</v>
       </c>
       <c r="G1395" t="n">
-        <v>10.8803424835205</v>
+        <v>10.8803434371948</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1397" t="n">
-        <v>10.8946905136108</v>
+        <v>10.8946914672852</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G1399" t="n">
-        <v>10.746431350708</v>
+        <v>10.7464303970337</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1409" t="n">
-        <v>10.4929552078247</v>
+        <v>10.4929542541504</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1413" t="n">
-        <v>10.9951248168945</v>
+        <v>10.9951257705688</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.2294702529907</v>
+        <v>11.229471206665</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1417" t="n">
-        <v>11.3203401565552</v>
+        <v>11.3203392028809</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.3442506790161</v>
+        <v>11.3442516326904</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1422" t="n">
-        <v>11.4303388595581</v>
+        <v>11.4303379058838</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>11.9549999237061</v>
       </c>
       <c r="G1425" t="n">
-        <v>11.4351215362549</v>
+        <v>11.4351205825806</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1427" t="n">
-        <v>11.5451202392578</v>
+        <v>11.5451192855835</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>11.5690326690674</v>
+        <v>11.5690336227417</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1433" t="n">
-        <v>11.0859928131104</v>
+        <v>11.085991859436</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>11.8249998092651</v>
       </c>
       <c r="G1434" t="n">
-        <v>11.3107738494873</v>
+        <v>11.310772895813</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1436" t="n">
-        <v>11.2103404998779</v>
+        <v>11.2103395462036</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>11.7049999237061</v>
       </c>
       <c r="G1437" t="n">
-        <v>11.1959924697876</v>
+        <v>11.1959915161133</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1445" t="n">
-        <v>11.3203401565552</v>
+        <v>11.3203392028809</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1446" t="n">
-        <v>11.4016427993774</v>
+        <v>11.4016437530518</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1447" t="n">
-        <v>11.3394689559937</v>
+        <v>11.339469909668</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1449" t="n">
-        <v>11.3394689559937</v>
+        <v>11.339469909668</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>11.75</v>
       </c>
       <c r="G1451" t="n">
-        <v>11.2390356063843</v>
+        <v>11.2390365600586</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G1459" t="n">
-        <v>11.5833797454834</v>
+        <v>11.5833806991577</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1464" t="n">
-        <v>11.5690326690674</v>
+        <v>11.5690336227417</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>12.375</v>
       </c>
       <c r="G1467" t="n">
-        <v>11.836856842041</v>
+        <v>11.8368558883667</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1471" t="n">
-        <v>11.9659862518311</v>
+        <v>11.9659852981567</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1473" t="n">
-        <v>12.3677215576172</v>
+        <v>12.3677225112915</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1476" t="n">
-        <v>12.3677215576172</v>
+        <v>12.3677225112915</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1482" t="n">
-        <v>11.8320732116699</v>
+        <v>11.8320741653442</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>12.4350004196167</v>
       </c>
       <c r="G1484" t="n">
-        <v>11.8942489624023</v>
+        <v>11.894248008728</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1492" t="n">
-        <v>12.2290267944336</v>
+        <v>12.2290258407593</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1494" t="n">
-        <v>12.4538087844849</v>
+        <v>12.4538078308105</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>12.7694568634033</v>
+        <v>12.7694578170776</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G1498" t="n">
-        <v>12.7455434799194</v>
+        <v>12.7455444335938</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1501" t="n">
-        <v>12.4059829711914</v>
+        <v>12.4059839248657</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G1503" t="n">
-        <v>12.2959823608398</v>
+        <v>12.2959833145142</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1507" t="n">
-        <v>12.1572885513306</v>
+        <v>12.1572895050049</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>13.2550001144409</v>
       </c>
       <c r="G1510" t="n">
-        <v>12.6785898208618</v>
+        <v>12.6785888671875</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1511" t="n">
-        <v>12.4059829711914</v>
+        <v>12.4059839248657</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>12.9849996566772</v>
       </c>
       <c r="G1512" t="n">
-        <v>12.4203290939331</v>
+        <v>12.4203300476074</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.3964166641235</v>
+        <v>12.3964176177979</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1514" t="n">
-        <v>12.3677215576172</v>
+        <v>12.3677225112915</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>12.7449998855591</v>
       </c>
       <c r="G1515" t="n">
-        <v>12.190767288208</v>
+        <v>12.1907663345337</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>12.0185947418213</v>
+        <v>12.018593788147</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>12.1859836578369</v>
+        <v>12.1859846115112</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>12.8050003051758</v>
       </c>
       <c r="G1523" t="n">
-        <v>12.248158454895</v>
+        <v>12.2481575012207</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G1526" t="n">
-        <v>12.2959823608398</v>
+        <v>12.2959833145142</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1532" t="n">
-        <v>11.5785970687866</v>
+        <v>11.5785980224609</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G1536" t="n">
-        <v>10.985559463501</v>
+        <v>10.9855585098267</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>11.375</v>
       </c>
       <c r="G1539" t="n">
-        <v>10.8803424835205</v>
+        <v>10.8803434371948</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>11.3950004577637</v>
       </c>
       <c r="G1541" t="n">
-        <v>10.8994750976562</v>
+        <v>10.8994741439819</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.6507797241211</v>
+        <v>10.6507806777954</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>11.0150003433228</v>
       </c>
       <c r="G1543" t="n">
-        <v>10.5359983444214</v>
+        <v>10.5359992980957</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1547" t="n">
-        <v>10.6077375411987</v>
+        <v>10.6077365875244</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>10.3686094284058</v>
+        <v>10.3686084747314</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>10.4849996566772</v>
       </c>
       <c r="G1558" t="n">
-        <v>10.0290460586548</v>
+        <v>10.0290451049805</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1559" t="n">
-        <v>10.0146989822388</v>
+        <v>10.0146980285645</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G1561" t="n">
-        <v>10.1103487014771</v>
+        <v>10.1103496551514</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G1572" t="n">
-        <v>8.70618915557861</v>
+        <v>8.7061882019043</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>9.41600036621094</v>
       </c>
       <c r="G1574" t="n">
-        <v>9.0065336227417</v>
+        <v>9.00653266906738</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G1575" t="n">
-        <v>8.85540390014648</v>
+        <v>8.8554048538208</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.81905555725098</v>
+        <v>8.81905651092529</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G1577" t="n">
-        <v>8.86305618286133</v>
+        <v>8.86305522918701</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>9.4407901763916</v>
+        <v>9.44078922271729</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>9.60339736938477</v>
+        <v>9.60339641571045</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1583" t="n">
-        <v>9.5364408493042</v>
+        <v>9.53644180297852</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G1589" t="n">
-        <v>10.1246967315674</v>
+        <v>10.1246976852417</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1595" t="n">
-        <v>10.34947681427</v>
+        <v>10.3494777679443</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>10.7250003814697</v>
       </c>
       <c r="G1597" t="n">
-        <v>10.2586097717285</v>
+        <v>10.2586088180542</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>10.4549999237061</v>
       </c>
       <c r="G1601" t="n">
-        <v>10.0575218200684</v>
+        <v>10.0575227737427</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1607" t="n">
-        <v>10.264349937439</v>
+        <v>10.2643489837646</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>10.4750003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>10.0767621994019</v>
+        <v>10.0767631530762</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G1612" t="n">
-        <v>9.9132251739502</v>
+        <v>9.91322612762451</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1615" t="n">
-        <v>9.19847297668457</v>
+        <v>9.19847202301025</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1617" t="n">
-        <v>9.54286289215088</v>
+        <v>9.54286193847656</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>10.2449998855591</v>
       </c>
       <c r="G1620" t="n">
-        <v>9.85550594329834</v>
+        <v>9.85550689697266</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>9.76411819458008</v>
+        <v>9.76411724090576</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.82800006866455</v>
       </c>
       <c r="G1622" t="n">
-        <v>9.45435905456543</v>
+        <v>9.45436000823975</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>9.58600044250488</v>
       </c>
       <c r="G1624" t="n">
-        <v>9.22155952453613</v>
+        <v>9.22156047821045</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>9.84799957275391</v>
       </c>
       <c r="G1625" t="n">
-        <v>9.47359848022461</v>
+        <v>9.47359943389893</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1626" t="n">
-        <v>9.26388645172119</v>
+        <v>9.26388740539551</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>9.69799995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>9.32930183410645</v>
+        <v>9.32930088043213</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G1632" t="n">
-        <v>9.37547874450684</v>
+        <v>9.37547779083252</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.92599964141846</v>
       </c>
       <c r="G1633" t="n">
-        <v>9.54863357543945</v>
+        <v>9.54863452911377</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G1634" t="n">
-        <v>9.519775390625</v>
+        <v>9.51977443695068</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G1636" t="n">
-        <v>9.53516578674316</v>
+        <v>9.53516674041748</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>9.25</v>
       </c>
       <c r="G1639" t="n">
-        <v>8.89833450317383</v>
+        <v>8.89833354949951</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>9.42199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>9.06379413604736</v>
+        <v>9.06379508972168</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>9.33199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>8.97721576690674</v>
+        <v>8.97721672058105</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>9.75</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.3793249130249</v>
+        <v>9.37932586669922</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G1645" t="n">
-        <v>9.42357635498047</v>
+        <v>9.42357540130615</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G1651" t="n">
-        <v>9.76892757415771</v>
+        <v>9.76892852783203</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G1654" t="n">
-        <v>9.57941722869873</v>
+        <v>9.57941818237305</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G1657" t="n">
-        <v>9.80740642547607</v>
+        <v>9.80740547180176</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1658" t="n">
-        <v>9.8506965637207</v>
+        <v>9.85069751739502</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G1659" t="n">
-        <v>9.9132251739502</v>
+        <v>9.91322612762451</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G1661" t="n">
-        <v>9.9132251739502</v>
+        <v>9.91322612762451</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>10.5450000762939</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.144100189209</v>
+        <v>10.1441011428833</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>10.375</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.98056411743164</v>
+        <v>9.98056507110596</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1669" t="n">
-        <v>10.0815706253052</v>
+        <v>10.0815715789795</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>10.664999961853</v>
       </c>
       <c r="G1670" t="n">
-        <v>10.259539604187</v>
+        <v>10.2595386505127</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G1675" t="n">
-        <v>10.2114381790161</v>
+        <v>10.2114391326904</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1680" t="n">
-        <v>9.82664680480957</v>
+        <v>9.82664585113525</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>10.0450000762939</v>
       </c>
       <c r="G1681" t="n">
-        <v>9.66310977935791</v>
+        <v>9.66310882568359</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G1688" t="n">
-        <v>9.99499416351318</v>
+        <v>9.9949951171875</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G1689" t="n">
-        <v>9.9132251739502</v>
+        <v>9.91322612762451</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G1690" t="n">
-        <v>9.76892757415771</v>
+        <v>9.76892852783203</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G1691" t="n">
-        <v>9.99980354309082</v>
+        <v>9.99980449676514</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1695" t="n">
-        <v>9.76411819458008</v>
+        <v>9.76411724090576</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>9.80799961090088</v>
       </c>
       <c r="G1696" t="n">
-        <v>9.43511962890625</v>
+        <v>9.43512058258057</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>9.42800045013428</v>
       </c>
       <c r="G1699" t="n">
-        <v>9.06956768035889</v>
+        <v>9.06956672668457</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>9.34799957275391</v>
       </c>
       <c r="G1701" t="n">
-        <v>8.99260807037354</v>
+        <v>8.99260711669922</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>9.42199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>9.06379413604736</v>
+        <v>9.06379508972168</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>9.25</v>
       </c>
       <c r="G1709" t="n">
-        <v>8.89833450317383</v>
+        <v>8.89833354949951</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G1713" t="n">
-        <v>8.55586814880371</v>
+        <v>8.55586910247803</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>9.0959997177124</v>
       </c>
       <c r="G1716" t="n">
-        <v>8.75018882751465</v>
+        <v>8.75018978118896</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G1717" t="n">
-        <v>8.59242343902588</v>
+        <v>8.5924243927002</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>9.0959997177124</v>
       </c>
       <c r="G1721" t="n">
-        <v>8.75018882751465</v>
+        <v>8.75018978118896</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G1722" t="n">
-        <v>8.65591430664062</v>
+        <v>8.65591526031494</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G1730" t="n">
-        <v>8.70786190032959</v>
+        <v>8.70786094665527</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G1732" t="n">
-        <v>8.59242343902588</v>
+        <v>8.5924243927002</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>8.6540002822876</v>
       </c>
       <c r="G1733" t="n">
-        <v>8.32499313354492</v>
+        <v>8.32499217987061</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>9.00599956512451</v>
       </c>
       <c r="G1736" t="n">
-        <v>8.66361045837402</v>
+        <v>8.66360950469971</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G1738" t="n">
-        <v>8.57703304290771</v>
+        <v>8.5770320892334</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G1743" t="n">
-        <v>8.95797634124756</v>
+        <v>8.95797729492188</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1744" t="n">
-        <v>8.97914028167725</v>
+        <v>8.97913932800293</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G1748" t="n">
-        <v>9.42357635498047</v>
+        <v>9.42357540130615</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1750" t="n">
-        <v>9.35046577453613</v>
+        <v>9.35046672821045</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1751" t="n">
-        <v>9.42165088653564</v>
+        <v>9.42165184020996</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G1752" t="n">
-        <v>9.58903694152832</v>
+        <v>9.58903789520264</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G1773" t="n">
-        <v>9.44089221954346</v>
+        <v>9.44089317321777</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>9.58600044250488</v>
       </c>
       <c r="G1778" t="n">
-        <v>9.22155952453613</v>
+        <v>9.22156047821045</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1780" t="n">
-        <v>9.2812032699585</v>
+        <v>9.28120231628418</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>9.48400020599365</v>
       </c>
       <c r="G1782" t="n">
-        <v>9.12343788146973</v>
+        <v>9.12343692779541</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G1793" t="n">
-        <v>9.519775390625</v>
+        <v>9.51977443695068</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>9.84799957275391</v>
       </c>
       <c r="G1796" t="n">
-        <v>9.47359848022461</v>
+        <v>9.47359943389893</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>9.94400024414062</v>
       </c>
       <c r="G1799" t="n">
-        <v>9.56594944000244</v>
+        <v>9.56595039367676</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1801" t="n">
-        <v>9.30236625671387</v>
+        <v>9.30236721038818</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G1803" t="n">
-        <v>9.29659366607666</v>
+        <v>9.29659461975098</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>9.82800006866455</v>
       </c>
       <c r="G1804" t="n">
-        <v>9.45435905456543</v>
+        <v>9.45436000823975</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G1810" t="n">
-        <v>9.76892757415771</v>
+        <v>9.76892852783203</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1811" t="n">
-        <v>9.82664680480957</v>
+        <v>9.82664585113525</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G1812" t="n">
-        <v>9.68234920501709</v>
+        <v>9.68234825134277</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>10.1489105224609</v>
+        <v>10.1489114761353</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1823" t="n">
-        <v>10.2162494659424</v>
+        <v>10.2162485122681</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>10.4549999237061</v>
       </c>
       <c r="G1825" t="n">
-        <v>10.0575218200684</v>
+        <v>10.0575227737427</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G1827" t="n">
-        <v>10.3797874450684</v>
+        <v>10.379786491394</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1828" t="n">
-        <v>10.3124485015869</v>
+        <v>10.3124475479126</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1830" t="n">
-        <v>10.2354898452759</v>
+        <v>10.2354888916016</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1831" t="n">
-        <v>10.2354898452759</v>
+        <v>10.2354888916016</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1834" t="n">
-        <v>10.264349937439</v>
+        <v>10.2643489837646</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>10.7250003814697</v>
       </c>
       <c r="G1835" t="n">
-        <v>10.3172588348389</v>
+        <v>10.3172578811646</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1845" t="n">
-        <v>10.716480255127</v>
+        <v>10.7164812088013</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>11.3950004577637</v>
       </c>
       <c r="G1850" t="n">
-        <v>10.9617853164673</v>
+        <v>10.9617862701416</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G1851" t="n">
-        <v>11.077223777771</v>
+        <v>11.0772228240967</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1852" t="n">
-        <v>11.0579843521118</v>
+        <v>11.0579833984375</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>11.5550003051758</v>
       </c>
       <c r="G1856" t="n">
-        <v>11.1157035827637</v>
+        <v>11.1157026290894</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1858" t="n">
-        <v>11.1782321929932</v>
+        <v>11.1782312393188</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>11.6450004577637</v>
       </c>
       <c r="G1859" t="n">
-        <v>11.2022819519043</v>
+        <v>11.20228099823</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>5.96000003814697</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>5901277</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>6.11600017547607</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>5.96000003814697</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>6.07600021362305</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>6.07600021362305</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>6.06400012969971</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>6.03200006484985</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>4323385</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>6.12200021743774</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>6.01800012588501</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>6.09000015258789</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>6.08599996566772</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>4538412</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>6.13199996948242</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>6.04099988937378</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>6.08599996566772</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>6.08599996566772</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>6.11600017547607</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>6934854</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>6.13600015640259</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>6.09200000762939</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>6.09200000762939</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>6.07200002670288</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>2763388</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>6.19199991226196</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>5734440</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>6.30200004577637</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>6.09200000762939</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>6.09200000762939</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>6.27400016784668</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.87750005722046</v>
       </c>
       <c r="G2" t="n">
-        <v>3.54454159736633</v>
+        <v>3.54454183578491</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60396027565002</v>
+        <v>3.60395979881287</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.8824999332428</v>
       </c>
       <c r="G4" t="n">
-        <v>3.54911184310913</v>
+        <v>3.54911208152771</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.79250001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.46684050559998</v>
+        <v>3.46684074401855</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.78250002861023</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45769929885864</v>
+        <v>3.45769953727722</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5742506980896</v>
+        <v>3.57425093650818</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>3.51940298080444</v>
+        <v>3.51940274238586</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>3.47369647026062</v>
+        <v>3.47369623184204</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.75250005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43027544021606</v>
+        <v>3.43027496337891</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.84249997138977</v>
       </c>
       <c r="G13" t="n">
-        <v>3.51254677772522</v>
+        <v>3.5125470161438</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G14" t="n">
-        <v>3.38228392601013</v>
+        <v>3.38228321075439</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.77749991416931</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45312809944153</v>
+        <v>3.45312833786011</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.8824999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>3.54911184310913</v>
+        <v>3.54911208152771</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>3.58796238899231</v>
+        <v>3.58796262741089</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>3.61081647872925</v>
+        <v>3.61081576347351</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>3.51483178138733</v>
+        <v>3.51483201980591</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03249979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6862313747406</v>
+        <v>3.68623161315918</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6656641960144</v>
+        <v>3.66566395759583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G23" t="n">
-        <v>3.65195178985596</v>
+        <v>3.65195202827454</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5742506980896</v>
+        <v>3.57425093650818</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G25" t="n">
-        <v>3.41884851455688</v>
+        <v>3.41884875297546</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>3.39142441749573</v>
+        <v>3.39142465591431</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.67249989509583</v>
       </c>
       <c r="G29" t="n">
-        <v>3.35714411735535</v>
+        <v>3.3571445941925</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.52250003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.22002530097961</v>
+        <v>3.22002553939819</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G33" t="n">
-        <v>3.19488620758057</v>
+        <v>3.19488668441772</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.27258729934692</v>
+        <v>3.2725875377655</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.54250001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>3.23830771446228</v>
+        <v>3.23830795288086</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G36" t="n">
-        <v>3.26801705360413</v>
+        <v>3.26801681518555</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.62249994277954</v>
       </c>
       <c r="G38" t="n">
-        <v>3.3114378452301</v>
+        <v>3.31143832206726</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>3.27258729934692</v>
+        <v>3.2725875377655</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35485911369324</v>
+        <v>3.3548595905304</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.625</v>
       </c>
       <c r="G42" t="n">
-        <v>3.31372308731079</v>
+        <v>3.31372332572937</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75250005722046</v>
       </c>
       <c r="G43" t="n">
-        <v>3.43027544021606</v>
+        <v>3.43027496337891</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>3.478266954422</v>
+        <v>3.47826719284058</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>3.55139780044556</v>
+        <v>3.55139756202698</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.89249992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.55825352668762</v>
+        <v>3.55825328826904</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>3.51026153564453</v>
+        <v>3.51026129722595</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>3.56053853034973</v>
+        <v>3.56053900718689</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.58339166641235</v>
+        <v>3.58339214324951</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>3.81649565696716</v>
+        <v>3.81649541854858</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.26249980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89648246765137</v>
+        <v>3.89648127555847</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.31750011444092</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94675898551941</v>
+        <v>3.94675874710083</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.36250019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.9878945350647</v>
+        <v>3.98789525032043</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.34749984741211</v>
       </c>
       <c r="G56" t="n">
-        <v>3.97418308258057</v>
+        <v>3.97418212890625</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G57" t="n">
-        <v>3.98103880882263</v>
+        <v>3.98103904724121</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>3.97646808624268</v>
+        <v>3.97646880149841</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>3.95818591117859</v>
+        <v>3.95818567276001</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.95818591117859</v>
+        <v>3.95818567276001</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>4.03131628036499</v>
+        <v>4.03131580352783</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.39249992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>4.01531887054443</v>
+        <v>4.01531934738159</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.35249996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>3.9787540435791</v>
+        <v>3.97875428199768</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G65" t="n">
-        <v>4.02217483520508</v>
+        <v>4.02217435836792</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>3.96275663375854</v>
+        <v>3.9627571105957</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>3.96275663375854</v>
+        <v>3.9627571105957</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>3.93533253669739</v>
+        <v>3.93533182144165</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.25</v>
       </c>
       <c r="G71" t="n">
-        <v>3.88505530357361</v>
+        <v>3.88505506515503</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91476321220398</v>
+        <v>3.91476464271545</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.3125</v>
       </c>
       <c r="G73" t="n">
-        <v>3.94218754768372</v>
+        <v>3.94218778610229</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.24249982833862</v>
       </c>
       <c r="G74" t="n">
-        <v>3.87819981575012</v>
+        <v>3.87819862365723</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.25250005722046</v>
       </c>
       <c r="G75" t="n">
-        <v>3.88734126091003</v>
+        <v>3.8873405456543</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.34250020980835</v>
       </c>
       <c r="G76" t="n">
-        <v>3.96961331367493</v>
+        <v>3.96961283683777</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.36749982833862</v>
       </c>
       <c r="G77" t="n">
-        <v>3.99246501922607</v>
+        <v>3.99246549606323</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G78" t="n">
-        <v>3.9490442276001</v>
+        <v>3.94904446601868</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>3.8987672328949</v>
+        <v>3.89876651763916</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.92619132995605</v>
+        <v>3.9261908531189</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.33750009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>3.96504163742065</v>
+        <v>3.96504235267639</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.27750015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>3.91019415855408</v>
+        <v>3.9101939201355</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G84" t="n">
-        <v>3.85306096076965</v>
+        <v>3.85306072235107</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G85" t="n">
-        <v>3.83934903144836</v>
+        <v>3.83934879302979</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.17749977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>3.81878113746643</v>
+        <v>3.81878042221069</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.23250007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.86905789375305</v>
+        <v>3.86905813217163</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.30249977111816</v>
       </c>
       <c r="G92" t="n">
-        <v>3.93304657936096</v>
+        <v>3.93304681777954</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.90790867805481</v>
+        <v>3.90790843963623</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>3.90333724021912</v>
+        <v>3.90333795547485</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.83020782470703</v>
+        <v>3.83020758628845</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G97" t="n">
-        <v>3.83477807044983</v>
+        <v>3.83477735519409</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.83455586433411</v>
+        <v>3.83455634117126</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.29250001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.96622467041016</v>
+        <v>3.96622443199158</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G103" t="n">
-        <v>4.01473379135132</v>
+        <v>4.01473426818848</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.35249996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.02166414260864</v>
+        <v>4.0216646194458</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>4.03783321380615</v>
+        <v>4.03783369064331</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.34250020980835</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0124249458313</v>
+        <v>4.01242446899414</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>4.02859401702881</v>
+        <v>4.02859449386597</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.03783321380615</v>
+        <v>4.03783369064331</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.35750007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>4.02628374099731</v>
+        <v>4.02628421783447</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G111" t="n">
-        <v>4.0516939163208</v>
+        <v>4.05169439315796</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>4.01935386657715</v>
+        <v>4.01935434341431</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G113" t="n">
-        <v>3.95929527282715</v>
+        <v>3.95929479598999</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.16249990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.84610605239868</v>
+        <v>3.8461058139801</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G115" t="n">
-        <v>3.79759645462036</v>
+        <v>3.79759693145752</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.11250019073486</v>
       </c>
       <c r="G116" t="n">
-        <v>3.7999062538147</v>
+        <v>3.79990673065186</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>3.80683612823486</v>
+        <v>3.80683660507202</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.94543433189392</v>
+        <v>3.94543480873108</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.27250003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>3.94774460792542</v>
+        <v>3.94774389266968</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89923524856567</v>
+        <v>3.89923477172852</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.3274998664856</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99856448173523</v>
+        <v>3.99856472015381</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82762598991394</v>
+        <v>3.82762551307678</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>3.82993602752686</v>
+        <v>3.82993626594543</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.30749988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.98008513450623</v>
+        <v>3.98008489608765</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.35750007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>4.02628374099731</v>
+        <v>4.02628421783447</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>4.10251235961914</v>
+        <v>4.10251331329346</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.4225001335144</v>
       </c>
       <c r="G130" t="n">
-        <v>4.08634376525879</v>
+        <v>4.08634424209595</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.26749992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>3.94312500953674</v>
+        <v>3.94312477111816</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>4.09789276123047</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.43249988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>4.09558296203613</v>
+        <v>4.09558391571045</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G137" t="n">
-        <v>4.01473379135132</v>
+        <v>4.01473426818848</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.38749980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>4.05400323867798</v>
+        <v>4.05400371551514</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.33750009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>4.00780487060547</v>
+        <v>4.00780344009399</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.40749979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>4.0724835395813</v>
+        <v>4.07248258590698</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07941341400146</v>
+        <v>4.07941389083862</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>4.12099313735962</v>
+        <v>4.12099266052246</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.4375</v>
       </c>
       <c r="G143" t="n">
-        <v>4.10020208358765</v>
+        <v>4.10020351409912</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.49749994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15564250946045</v>
+        <v>4.15564203262329</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.2272515296936</v>
+        <v>4.22725105285645</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>4.23187160491943</v>
+        <v>4.23187112808228</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.61749982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>4.26652002334595</v>
+        <v>4.26652050018311</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.625</v>
       </c>
       <c r="G150" t="n">
-        <v>4.27345037460327</v>
+        <v>4.27345132827759</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G154" t="n">
-        <v>4.45362949371338</v>
+        <v>4.45362901687622</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>4.37046957015991</v>
+        <v>4.37047004699707</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.41204881668091</v>
+        <v>4.41204929351807</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>4.6014666557312</v>
+        <v>4.60146760940552</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.89249992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>4.52061796188354</v>
+        <v>4.5206184387207</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G161" t="n">
-        <v>4.4905891418457</v>
+        <v>4.49058818817139</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G162" t="n">
-        <v>4.49520874023438</v>
+        <v>4.49520921707153</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.90749979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>4.53447818756104</v>
+        <v>4.53447771072388</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.52754878997803</v>
+        <v>4.52754831314087</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>4.55064821243286</v>
+        <v>4.5506477355957</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.87750005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>4.50675916671753</v>
+        <v>4.50675868988037</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>4.63380718231201</v>
+        <v>4.6338062286377</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>4.6014666557312</v>
+        <v>4.60146760940552</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>4.63842678070068</v>
+        <v>4.63842630386353</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G177" t="n">
-        <v>4.53216791152954</v>
+        <v>4.53216886520386</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>4.39818954467773</v>
+        <v>4.39819049835205</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>4.3335108757019</v>
+        <v>4.33350992202759</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>4.36584949493408</v>
+        <v>4.36584997177124</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.80249977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>4.43745946884155</v>
+        <v>4.43745851516724</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>4.42359972000122</v>
+        <v>4.42360019683838</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G184" t="n">
-        <v>4.44900894165039</v>
+        <v>4.44900941848755</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G186" t="n">
-        <v>4.42128896713257</v>
+        <v>4.42128849029541</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G187" t="n">
-        <v>4.63842678070068</v>
+        <v>4.63842630386353</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>4.58298778533936</v>
+        <v>4.58298683166504</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>4.66152715682983</v>
+        <v>4.66152667999268</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>4.64304733276367</v>
+        <v>4.64304685592651</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>4.63380718231201</v>
+        <v>4.6338062286377</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5</v>
       </c>
       <c r="G194" t="n">
-        <v>4.61994743347168</v>
+        <v>4.61994647979736</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>4.58298778533936</v>
+        <v>4.58298683166504</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51830863952637</v>
+        <v>4.51830768585205</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>4.40742969512939</v>
+        <v>4.40743064880371</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G199" t="n">
-        <v>4.42359972000122</v>
+        <v>4.42360019683838</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G202" t="n">
-        <v>4.37970924377441</v>
+        <v>4.37970972061157</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G204" t="n">
-        <v>4.37508964538574</v>
+        <v>4.3750901222229</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>4.45824956893921</v>
+        <v>4.45824909210205</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.78749990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>4.42359972000122</v>
+        <v>4.42360019683838</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G208" t="n">
-        <v>4.39818954467773</v>
+        <v>4.39819049835205</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>4.30579042434692</v>
+        <v>4.30579090118408</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G212" t="n">
-        <v>4.26421070098877</v>
+        <v>4.26421117782593</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>4.24111223220825</v>
+        <v>4.24111175537109</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.58750009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>4.23880100250244</v>
+        <v>4.2388014793396</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G216" t="n">
-        <v>4.14409255981445</v>
+        <v>4.14409351348877</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>4.09789276123047</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G218" t="n">
-        <v>4.03321361541748</v>
+        <v>4.03321313858032</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G222" t="n">
-        <v>3.8969259262085</v>
+        <v>3.89692544937134</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>3.894615650177</v>
+        <v>3.89461517333984</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.39750003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>4.06324338912964</v>
+        <v>4.06324434280396</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G226" t="n">
-        <v>3.95698404312134</v>
+        <v>3.9569845199585</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.4225001335144</v>
       </c>
       <c r="G228" t="n">
-        <v>4.08634376525879</v>
+        <v>4.08634424209595</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>4.09789276123047</v>
+        <v>4.09789228439331</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>4.14871215820312</v>
+        <v>4.14871263504028</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>4.12561368942261</v>
+        <v>4.12561321258545</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G233" t="n">
-        <v>4.18567228317261</v>
+        <v>4.18567180633545</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.14871215820312</v>
+        <v>4.14871263504028</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>4.20415163040161</v>
+        <v>4.20415258407593</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>4.12099313735962</v>
+        <v>4.12099266052246</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.50750017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>4.16488218307495</v>
+        <v>4.16488265991211</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>4.23187160491943</v>
+        <v>4.23187112808228</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.52750015258789</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18336296081543</v>
+        <v>4.18336248397827</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>4.25497102737427</v>
+        <v>4.25497150421143</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.65250015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>4.29886102676392</v>
+        <v>4.2988600730896</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G245" t="n">
-        <v>4.30579042434692</v>
+        <v>4.30579090118408</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G246" t="n">
-        <v>4.22494173049927</v>
+        <v>4.22494268417358</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>4.21339130401611</v>
+        <v>4.21339178085327</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>4.23649120330811</v>
+        <v>4.23649168014526</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>4.30579042434692</v>
+        <v>4.30579090118408</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.60750007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>4.25728130340576</v>
+        <v>4.25728178024292</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>4.24111223220825</v>
+        <v>4.24111175537109</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>4.29193162918091</v>
+        <v>4.29192972183228</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>4.29193162918091</v>
+        <v>4.29192972183228</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G255" t="n">
-        <v>4.28269147872925</v>
+        <v>4.28269052505493</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.27806997299194</v>
+        <v>4.27807140350342</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>4.29193162918091</v>
+        <v>4.29192972183228</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>4.27806997299194</v>
+        <v>4.27807140350342</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>4.29655075073242</v>
+        <v>4.29655122756958</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>4.30579042434692</v>
+        <v>4.30579090118408</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G267" t="n">
-        <v>4.30579042434692</v>
+        <v>4.30579090118408</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.66249990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>4.3080997467041</v>
+        <v>4.30810022354126</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.65749979019165</v>
       </c>
       <c r="G269" t="n">
-        <v>4.30348062515259</v>
+        <v>4.30348014831543</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G270" t="n">
-        <v>4.40280961990356</v>
+        <v>4.40281009674072</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G271" t="n">
-        <v>4.44900894165039</v>
+        <v>4.44900941848755</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.75250005722046</v>
       </c>
       <c r="G272" t="n">
-        <v>4.39125919342041</v>
+        <v>4.39125967025757</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.71750020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.35892057418823</v>
+        <v>4.35892009735107</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.72749996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36816024780273</v>
+        <v>4.36815881729126</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>4.40049886703491</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>4.40049886703491</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.76249980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>4.40049886703491</v>
+        <v>4.40049982070923</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.69250011444092</v>
       </c>
       <c r="G278" t="n">
-        <v>4.33581972122192</v>
+        <v>4.33582019805908</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.72249984741211</v>
       </c>
       <c r="G283" t="n">
-        <v>4.3635401725769</v>
+        <v>4.36353969573975</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>4.40742969512939</v>
+        <v>4.40743064880371</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G286" t="n">
-        <v>4.4259090423584</v>
+        <v>4.42590951919556</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.76749992370605</v>
       </c>
       <c r="G287" t="n">
-        <v>4.4051194190979</v>
+        <v>4.40511894226074</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.82250022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>4.45594024658203</v>
+        <v>4.45593929290771</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.82250022888184</v>
       </c>
       <c r="G289" t="n">
-        <v>4.45594024658203</v>
+        <v>4.45593929290771</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>4.4259090423584</v>
+        <v>4.42590951919556</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.84250020980835</v>
       </c>
       <c r="G291" t="n">
-        <v>4.47441864013672</v>
+        <v>4.47441959381104</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.83750009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>4.46979951858521</v>
+        <v>4.46979904174805</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G293" t="n">
-        <v>4.47672891616821</v>
+        <v>4.47672843933105</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.50906896591187</v>
+        <v>4.50906848907471</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>4.45362949371338</v>
+        <v>4.45362901687622</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.87750005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>4.50675916671753</v>
+        <v>4.50675868988037</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>4.41204881668091</v>
+        <v>4.41204929351807</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G300" t="n">
-        <v>4.4905891418457</v>
+        <v>4.49058818817139</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.85249996185303</v>
       </c>
       <c r="G301" t="n">
-        <v>4.48365831375122</v>
+        <v>4.48365926742554</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.87249994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>4.50213861465454</v>
+        <v>4.50213813781738</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.85249996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>4.48365831375122</v>
+        <v>4.48365926742554</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.80249977111816</v>
       </c>
       <c r="G305" t="n">
-        <v>4.43745946884155</v>
+        <v>4.43745851516724</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.88749980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.51599884033203</v>
+        <v>4.51599836349487</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.52754878997803</v>
+        <v>4.52754831314087</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>4.67076635360718</v>
+        <v>4.67076587677002</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>4.68462753295898</v>
+        <v>4.68462610244751</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G314" t="n">
-        <v>4.67076635360718</v>
+        <v>4.67076587677002</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>4.66152715682983</v>
+        <v>4.66152667999268</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.125</v>
       </c>
       <c r="G316" t="n">
-        <v>4.73544597625732</v>
+        <v>4.73544502258301</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.125</v>
       </c>
       <c r="G317" t="n">
-        <v>4.73544597625732</v>
+        <v>4.73544502258301</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>4.75854635238647</v>
+        <v>4.75854539871216</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G319" t="n">
-        <v>4.8232250213623</v>
+        <v>4.82322454452515</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8232250213623</v>
+        <v>4.82322454452515</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8740439414978</v>
+        <v>4.87404441833496</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>5.0218825340271</v>
+        <v>5.02188205718994</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.97568273544312</v>
+        <v>4.97568368911743</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>4.9710636138916</v>
+        <v>4.97106266021729</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G326" t="n">
-        <v>4.98030233383179</v>
+        <v>4.98030281066895</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>4.92024374008179</v>
+        <v>4.92024326324463</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.94334316253662</v>
+        <v>4.94334363937378</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.95258283615112</v>
+        <v>4.95258331298828</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G330" t="n">
-        <v>4.95720243453979</v>
+        <v>4.95720291137695</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>4.92024374008179</v>
+        <v>4.92024326324463</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8648042678833</v>
+        <v>4.86480379104614</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G333" t="n">
-        <v>4.90176343917847</v>
+        <v>4.90176391601562</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.25</v>
       </c>
       <c r="G334" t="n">
-        <v>4.85094404220581</v>
+        <v>4.85094499588013</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>4.89252376556396</v>
+        <v>4.89252424240112</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.09580135345459</v>
+        <v>5.09580230712891</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.5</v>
       </c>
       <c r="G339" t="n">
-        <v>5.08194160461426</v>
+        <v>5.08194255828857</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G340" t="n">
-        <v>5.01726198196411</v>
+        <v>5.01726245880127</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.5</v>
       </c>
       <c r="G343" t="n">
-        <v>5.08194160461426</v>
+        <v>5.08194255828857</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G344" t="n">
-        <v>5.17434120178223</v>
+        <v>5.17434024810791</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G345" t="n">
-        <v>5.1096625328064</v>
+        <v>5.10966157913208</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>5.58551549911499</v>
+        <v>5.58551597595215</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>5.51621627807617</v>
+        <v>5.51621675491333</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>5.53931570053101</v>
+        <v>5.53931665420532</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G351" t="n">
-        <v>5.59937524795532</v>
+        <v>5.59937572479248</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G352" t="n">
-        <v>5.49311780929565</v>
+        <v>5.49311685562134</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>5.52083683013916</v>
+        <v>5.520836353302</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>5.63633584976196</v>
+        <v>5.6363353729248</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G355" t="n">
-        <v>5.6084098815918</v>
+        <v>5.60841035842896</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>5.65495252609253</v>
+        <v>5.65495347976685</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.66426134109497</v>
+        <v>5.66426086425781</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G361" t="n">
-        <v>5.78061866760254</v>
+        <v>5.78061819076538</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G365" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093873977661</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G367" t="n">
-        <v>5.84577894210815</v>
+        <v>5.845778465271</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>5.77130889892578</v>
+        <v>5.7713098526001</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>5.66891622543335</v>
+        <v>5.66891574859619</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64564371109009</v>
+        <v>5.64564418792725</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>5.76200151443481</v>
+        <v>5.76200103759766</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G376" t="n">
-        <v>5.84112358093262</v>
+        <v>5.84112453460693</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>5.89232063293457</v>
+        <v>5.89231967926025</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G379" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G380" t="n">
-        <v>5.82716083526611</v>
+        <v>5.82716035842896</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>5.74338388442993</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>5.79923534393311</v>
+        <v>5.79923439025879</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>5.74338388442993</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734663009644</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>5.73873043060303</v>
+        <v>5.73872995376587</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>5.73407554626465</v>
+        <v>5.73407506942749</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.77130889892578</v>
+        <v>5.7713098526001</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>5.79923534393311</v>
+        <v>5.79923439025879</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>5.77130889892578</v>
+        <v>5.7713098526001</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.76665544509888</v>
+        <v>5.76665496826172</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.78061866760254</v>
+        <v>5.78061819076538</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>5.74803924560547</v>
+        <v>5.74803876876831</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>5.84112358093262</v>
+        <v>5.84112453460693</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G404" t="n">
-        <v>5.77130889892578</v>
+        <v>5.7713098526001</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>5.8364691734314</v>
+        <v>5.83646965026855</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>5.85508680343628</v>
+        <v>5.85508632659912</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G408" t="n">
-        <v>5.74803924560547</v>
+        <v>5.74803876876831</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G409" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218587875366</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G410" t="n">
-        <v>5.65960693359375</v>
+        <v>5.65960645675659</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.63168001174927</v>
+        <v>5.63168096542358</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>5.56652069091797</v>
+        <v>5.56652116775513</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G414" t="n">
-        <v>5.57582902908325</v>
+        <v>5.57582998275757</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.63168001174927</v>
+        <v>5.63168096542358</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G418" t="n">
-        <v>5.66891622543335</v>
+        <v>5.66891574859619</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G419" t="n">
-        <v>5.64564371109009</v>
+        <v>5.64564418792725</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G421" t="n">
-        <v>5.6735692024231</v>
+        <v>5.67356967926025</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G422" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218587875366</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G423" t="n">
-        <v>5.66426134109497</v>
+        <v>5.66426086425781</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>5.61306381225586</v>
+        <v>5.61306428909302</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>5.58048343658447</v>
+        <v>5.58048391342163</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>5.65960693359375</v>
+        <v>5.65960645675659</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G428" t="n">
-        <v>5.65029859542847</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64564371109009</v>
+        <v>5.64564418792725</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.125</v>
       </c>
       <c r="G430" t="n">
-        <v>5.70149564743042</v>
+        <v>5.70149517059326</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>5.74338388442993</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G436" t="n">
-        <v>5.73407554626465</v>
+        <v>5.73407506942749</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G437" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>5.65960693359375</v>
+        <v>5.65960645675659</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.125</v>
       </c>
       <c r="G440" t="n">
-        <v>5.70149564743042</v>
+        <v>5.70149517059326</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>5.68287801742554</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.68287801742554</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>5.69218683242798</v>
+        <v>5.69218587875366</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>5.79923534393311</v>
+        <v>5.79923439025879</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G449" t="n">
-        <v>5.74338388442993</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>5.78061866760254</v>
+        <v>5.78061819076538</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>5.76200151443481</v>
+        <v>5.76200103759766</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G453" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734663009644</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05522060394287</v>
+        <v>6.05522108078003</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G459" t="n">
-        <v>6.19019412994385</v>
+        <v>6.19019508361816</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>6.04591178894043</v>
+        <v>6.04591226577759</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>5.9388632774353</v>
+        <v>5.93886375427246</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>6.01333236694336</v>
+        <v>6.0133318901062</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>6.07383728027344</v>
+        <v>6.0738377571106</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>6.05522060394287</v>
+        <v>6.05522108078003</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>6.02264070510864</v>
+        <v>6.02264022827148</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>6.40429162979126</v>
+        <v>6.40429210662842</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>6.3251690864563</v>
+        <v>6.32516956329346</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>6.21346616744995</v>
+        <v>6.21346664428711</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>6.21812009811401</v>
+        <v>6.21812057495117</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>6.24139165878296</v>
+        <v>6.24139213562012</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>6.08314514160156</v>
+        <v>6.08314609527588</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G478" t="n">
-        <v>6.02264070510864</v>
+        <v>6.02264022827148</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>6.13899707794189</v>
+        <v>6.13899803161621</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G481" t="n">
-        <v>5.9481725692749</v>
+        <v>5.94817161560059</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G482" t="n">
-        <v>5.99471521377563</v>
+        <v>5.99471473693848</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>6.0086784362793</v>
+        <v>6.00867748260498</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>6.05522060394287</v>
+        <v>6.05522108078003</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>6.01798677444458</v>
+        <v>6.01798629760742</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>5.91559267044067</v>
+        <v>5.91559219360352</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G487" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351863861084</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G488" t="n">
-        <v>6.01798677444458</v>
+        <v>6.01798629760742</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>6.00402402877808</v>
+        <v>6.00402355194092</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>5.97144365310669</v>
+        <v>5.97144412994385</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>6.0878005027771</v>
+        <v>6.08780002593994</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>6.00402402877808</v>
+        <v>6.00402355194092</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G499" t="n">
-        <v>6.11572694778442</v>
+        <v>6.11572647094727</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G501" t="n">
-        <v>6.10641813278198</v>
+        <v>6.10641860961914</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>5.91559267044067</v>
+        <v>5.91559219360352</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>6.0366039276123</v>
+        <v>6.03660488128662</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.01333236694336</v>
+        <v>6.0133318901062</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.98075246810913</v>
+        <v>5.98075199127197</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G507" t="n">
-        <v>5.9481725692749</v>
+        <v>5.94817161560059</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.5</v>
       </c>
       <c r="G510" t="n">
-        <v>6.05056571960449</v>
+        <v>6.05056667327881</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>5.91559267044067</v>
+        <v>5.91559219360352</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G514" t="n">
-        <v>5.82716083526611</v>
+        <v>5.82716035842896</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>5.85974168777466</v>
+        <v>5.85974073410034</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G518" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>5.88766622543335</v>
+        <v>5.88766574859619</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G520" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>5.9388632774353</v>
+        <v>5.93886375427246</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>5.9388632774353</v>
+        <v>5.93886375427246</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G524" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.97609901428223</v>
+        <v>5.97609853744507</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>5.85043239593506</v>
+        <v>5.8504319190979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>5.88766622543335</v>
+        <v>5.88766574859619</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>5.98075246810913</v>
+        <v>5.98075199127197</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351863861084</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.92955541610718</v>
+        <v>5.92955493927002</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G535" t="n">
-        <v>6.02264070510864</v>
+        <v>6.02264022827148</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093873977661</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G537" t="n">
-        <v>5.76665544509888</v>
+        <v>5.76665496826172</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734663009644</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>5.58048343658447</v>
+        <v>5.58048391342163</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>5.65029859542847</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>5.74803924560547</v>
+        <v>5.74803876876831</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>5.68287801742554</v>
+        <v>5.6828784942627</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>5.78061866760254</v>
+        <v>5.78061819076538</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>5.81319761276245</v>
+        <v>5.81319808959961</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>5.79923534393311</v>
+        <v>5.79923439025879</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G548" t="n">
-        <v>5.83181524276733</v>
+        <v>5.83181381225586</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G550" t="n">
-        <v>5.79923534393311</v>
+        <v>5.79923439025879</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>5.49205303192139</v>
+        <v>5.49205255508423</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>5.34776973724365</v>
+        <v>5.34777021408081</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>5.42223787307739</v>
+        <v>5.42223834991455</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.52928733825684</v>
+        <v>5.52928781509399</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G562" t="n">
-        <v>5.6735692024231</v>
+        <v>5.67356967926025</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G563" t="n">
-        <v>5.65029859542847</v>
+        <v>5.65029907226562</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>5.64564371109009</v>
+        <v>5.64564418792725</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>5.67822360992432</v>
+        <v>5.67822408676147</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.74803924560547</v>
+        <v>5.74803876876831</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>5.74338388442993</v>
+        <v>5.74338436126709</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G573" t="n">
-        <v>5.77130889892578</v>
+        <v>5.7713098526001</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G575" t="n">
-        <v>5.6735692024231</v>
+        <v>5.67356967926025</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.84577894210815</v>
+        <v>5.845778465271</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G579" t="n">
-        <v>5.95282649993896</v>
+        <v>5.95282602310181</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G580" t="n">
-        <v>5.94351816177368</v>
+        <v>5.94351863861084</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G581" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G582" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.89697551727295</v>
+        <v>5.89697504043579</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G584" t="n">
-        <v>5.92490100860596</v>
+        <v>5.9249005317688</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G585" t="n">
-        <v>5.9388632774353</v>
+        <v>5.93886375427246</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G587" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G590" t="n">
-        <v>5.72942161560059</v>
+        <v>5.72942113876343</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.75734710693359</v>
+        <v>5.75734663009644</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G596" t="n">
-        <v>5.76665544509888</v>
+        <v>5.76665496826172</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G597" t="n">
-        <v>5.76665544509888</v>
+        <v>5.76665496826172</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>5.78061866760254</v>
+        <v>5.78061819076538</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G600" t="n">
-        <v>5.82716083526611</v>
+        <v>5.82716035842896</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>5.90162992477417</v>
+        <v>5.90162944793701</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>5.86904954910278</v>
+        <v>5.86904907226562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G606" t="n">
-        <v>5.91093778610229</v>
+        <v>5.91093873977661</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>5.90159273147583</v>
+        <v>5.90159225463867</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G611" t="n">
-        <v>5.99072599411011</v>
+        <v>5.99072647094727</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>6.09393358230591</v>
+        <v>6.09393405914307</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>5.99541759490967</v>
+        <v>5.99541711807251</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G615" t="n">
-        <v>5.99541759490967</v>
+        <v>5.99541711807251</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G616" t="n">
-        <v>5.99541759490967</v>
+        <v>5.99541711807251</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.375</v>
       </c>
       <c r="G617" t="n">
-        <v>5.98134326934814</v>
+        <v>5.9813437461853</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>6.17837572097778</v>
+        <v>6.17837619781494</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>6.29096555709839</v>
+        <v>6.29096651077271</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>6.4270133972168</v>
+        <v>6.42701244354248</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G628" t="n">
-        <v>6.59589767456055</v>
+        <v>6.59589719772339</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>6.52083730697632</v>
+        <v>6.52083683013916</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>6.47392559051514</v>
+        <v>6.47392463684082</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>6.40824699401855</v>
+        <v>6.40824747085571</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>6.4270133972168</v>
+        <v>6.42701244354248</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G635" t="n">
-        <v>6.55367565155029</v>
+        <v>6.55367660522461</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>6.47392559051514</v>
+        <v>6.47392463684082</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>6.60997104644775</v>
+        <v>6.6099705696106</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>6.60997104644775</v>
+        <v>6.6099705696106</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G639" t="n">
-        <v>6.72256135940552</v>
+        <v>6.72256183624268</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>6.67095756530762</v>
+        <v>6.67095708847046</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>6.72725296020508</v>
+        <v>6.72725248336792</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.375</v>
       </c>
       <c r="G642" t="n">
-        <v>6.919593334198</v>
+        <v>6.91959381103516</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>6.82107734680176</v>
+        <v>6.82107782363892</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G644" t="n">
-        <v>6.8163857460022</v>
+        <v>6.81638622283936</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G645" t="n">
-        <v>6.90552043914795</v>
+        <v>6.90552091598511</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>6.8632984161377</v>
+        <v>6.86329889297485</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G650" t="n">
-        <v>6.98996257781982</v>
+        <v>6.98996210098267</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G651" t="n">
-        <v>7.0697135925293</v>
+        <v>7.06971311569214</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>7.17292070388794</v>
+        <v>7.17292165756226</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>7.11193513870239</v>
+        <v>7.11193466186523</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>7.130699634552</v>
+        <v>7.13069915771484</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>6.84453392028809</v>
+        <v>6.84453439712524</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>6.89613723754883</v>
+        <v>6.89613771438599</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>6.90082883834839</v>
+        <v>6.90082836151123</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G662" t="n">
-        <v>6.8163857460022</v>
+        <v>6.81638622283936</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G666" t="n">
-        <v>6.93366765975952</v>
+        <v>6.93366718292236</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G668" t="n">
-        <v>6.9149022102356</v>
+        <v>6.91490268707275</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>7.07909536361694</v>
+        <v>7.0790958404541</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>7.30427646636963</v>
+        <v>7.30427598953247</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G673" t="n">
-        <v>7.18699550628662</v>
+        <v>7.18699407577515</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>7.13539171218872</v>
+        <v>7.13539123535156</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>7.16353940963745</v>
+        <v>7.16353845596313</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>7.13539171218872</v>
+        <v>7.13539123535156</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G680" t="n">
-        <v>7.14477348327637</v>
+        <v>7.14477300643921</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>7.130699634552</v>
+        <v>7.13069915771484</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>6.95243167877197</v>
+        <v>6.95243263244629</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156589508057</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>7.13539171218872</v>
+        <v>7.13539123535156</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>6.89613723754883</v>
+        <v>6.89613771438599</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G693" t="n">
-        <v>6.89613723754883</v>
+        <v>6.89613771438599</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>6.79762125015259</v>
+        <v>6.79762077331543</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>6.79762125015259</v>
+        <v>6.79762077331543</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>6.72725296020508</v>
+        <v>6.72725248336792</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>6.83984231948853</v>
+        <v>6.83984279632568</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>7.375</v>
       </c>
       <c r="G699" t="n">
-        <v>6.919593334198</v>
+        <v>6.91959381103516</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G701" t="n">
-        <v>6.88206338882446</v>
+        <v>6.88206386566162</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G707" t="n">
-        <v>6.53960227966309</v>
+        <v>6.53960180282593</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>6.23467111587524</v>
+        <v>6.2346715927124</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>6.10331630706787</v>
+        <v>6.10331678390503</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G711" t="n">
-        <v>6.02356576919556</v>
+        <v>6.0235652923584</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>5.95788717269897</v>
+        <v>5.95788764953613</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G713" t="n">
-        <v>6.12208080291748</v>
+        <v>6.12208127975464</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>6.22059726715088</v>
+        <v>6.2205982208252</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>6.17837572097778</v>
+        <v>6.17837619781494</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G716" t="n">
-        <v>6.23936176300049</v>
+        <v>6.2393627166748</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G717" t="n">
-        <v>6.24874401092529</v>
+        <v>6.24874448776245</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>6.0329475402832</v>
+        <v>6.03294801712036</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>6.29096555709839</v>
+        <v>6.29096651077271</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G721" t="n">
-        <v>6.21121501922607</v>
+        <v>6.21121549606323</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>6.21121501922607</v>
+        <v>6.21121549606323</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>6.25812721252441</v>
+        <v>6.25812768936157</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.75</v>
       </c>
       <c r="G726" t="n">
-        <v>6.33318853378296</v>
+        <v>6.33318758010864</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G728" t="n">
-        <v>6.66626644134521</v>
+        <v>6.66626596450806</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G729" t="n">
-        <v>6.90552043914795</v>
+        <v>6.90552091598511</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>6.88206338882446</v>
+        <v>6.88206386566162</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G731" t="n">
-        <v>6.97588872909546</v>
+        <v>6.97588920593262</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>7.18699550628662</v>
+        <v>7.18699407577515</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G734" t="n">
-        <v>7.01341867446899</v>
+        <v>7.01341915130615</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G735" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156589508057</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>7.21514225006104</v>
+        <v>7.21514272689819</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>7.20575952529907</v>
+        <v>7.20575904846191</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G738" t="n">
-        <v>7.00872707366943</v>
+        <v>7.00872659683228</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G739" t="n">
-        <v>6.92897653579712</v>
+        <v>6.92897701263428</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>6.89613723754883</v>
+        <v>6.89613771438599</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G741" t="n">
-        <v>7.04625844955444</v>
+        <v>7.04625797271729</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G742" t="n">
-        <v>6.98996257781982</v>
+        <v>6.98996210098267</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>6.89613723754883</v>
+        <v>6.89613771438599</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G745" t="n">
-        <v>6.8632984161377</v>
+        <v>6.86329889297485</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>6.92428493499756</v>
+        <v>6.92428541183472</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G750" t="n">
-        <v>7.00872707366943</v>
+        <v>7.00872659683228</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>7.25267267227173</v>
+        <v>7.25267219543457</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>7.5</v>
       </c>
       <c r="G753" t="n">
-        <v>7.03687524795532</v>
+        <v>7.03687572479248</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>7.09786224365234</v>
+        <v>7.09786081314087</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21514225006104</v>
+        <v>7.21514272689819</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G756" t="n">
-        <v>7.21045112609863</v>
+        <v>7.21045017242432</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>7.11193513870239</v>
+        <v>7.11193466186523</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>7.21045112609863</v>
+        <v>7.21045017242432</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>6.87737274169922</v>
+        <v>6.87737226486206</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G763" t="n">
-        <v>6.92897653579712</v>
+        <v>6.92897701263428</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>6.9149022102356</v>
+        <v>6.91490268707275</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G766" t="n">
-        <v>7.33711433410645</v>
+        <v>7.3371148109436</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>7.75</v>
       </c>
       <c r="G767" t="n">
-        <v>7.27143716812134</v>
+        <v>7.27143669128418</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>7.21983289718628</v>
+        <v>7.2198338508606</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>7.04156684875488</v>
+        <v>7.04156589508057</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>7.10724401473999</v>
+        <v>7.10724353790283</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>7.75</v>
       </c>
       <c r="G771" t="n">
-        <v>7.27143716812134</v>
+        <v>7.27143669128418</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>7.2292160987854</v>
+        <v>7.22921657562256</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>7.24328994750977</v>
+        <v>7.24329042434692</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G774" t="n">
-        <v>7.14477348327637</v>
+        <v>7.14477300643921</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G775" t="n">
-        <v>7.44032192230225</v>
+        <v>7.4403223991394</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G776" t="n">
-        <v>7.4919261932373</v>
+        <v>7.49192667007446</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G777" t="n">
-        <v>7.44032192230225</v>
+        <v>7.4403223991394</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>7.35118913650513</v>
+        <v>7.35118961334229</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G779" t="n">
-        <v>7.3793363571167</v>
+        <v>7.37933588027954</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>7.33242273330688</v>
+        <v>7.33242321014404</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>7.30896711349487</v>
+        <v>7.30896759033203</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G782" t="n">
-        <v>7.33711433410645</v>
+        <v>7.3371148109436</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>7.51069164276123</v>
+        <v>7.51069116592407</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>7.41686677932739</v>
+        <v>7.41686725616455</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G785" t="n">
-        <v>7.36057043075562</v>
+        <v>7.36057090759277</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>7.35118913650513</v>
+        <v>7.35118961334229</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>7.36057043075562</v>
+        <v>7.36057090759277</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>7.3746452331543</v>
+        <v>7.37464475631714</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>7.35587978363037</v>
+        <v>7.35588073730469</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G792" t="n">
-        <v>7.49661731719971</v>
+        <v>7.49661779403687</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G793" t="n">
-        <v>7.44970464706421</v>
+        <v>7.44970512390137</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G794" t="n">
-        <v>7.52945613861084</v>
+        <v>7.52945566177368</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G795" t="n">
-        <v>7.61859035491943</v>
+        <v>7.61858987808228</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>7.68895769119263</v>
+        <v>7.68895721435547</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>8.25</v>
       </c>
       <c r="G798" t="n">
-        <v>7.74056196212769</v>
+        <v>7.740562915802</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G803" t="n">
-        <v>7.83438920974731</v>
+        <v>7.83438873291016</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G804" t="n">
-        <v>7.71710586547852</v>
+        <v>7.71710681915283</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G805" t="n">
-        <v>7.86722707748413</v>
+        <v>7.86722612380981</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G806" t="n">
-        <v>7.89068174362183</v>
+        <v>7.89068222045898</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>7.40748357772827</v>
+        <v>7.40748310089111</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>7.43093919754028</v>
+        <v>7.43093967437744</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>7.6608099937439</v>
+        <v>7.66081094741821</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G814" t="n">
-        <v>7.65142869949341</v>
+        <v>7.65142822265625</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>7.78747415542603</v>
+        <v>7.78747606277466</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>7.91413879394531</v>
+        <v>7.91413736343384</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G817" t="n">
-        <v>7.8859920501709</v>
+        <v>7.88599109649658</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G818" t="n">
-        <v>7.9235200881958</v>
+        <v>7.92352056503296</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G819" t="n">
-        <v>7.94697713851929</v>
+        <v>7.9469780921936</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G820" t="n">
-        <v>8.07833385467529</v>
+        <v>8.07833290100098</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G821" t="n">
-        <v>7.94697713851929</v>
+        <v>7.9469780921936</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G823" t="n">
-        <v>8.31758499145508</v>
+        <v>8.31758689880371</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G824" t="n">
-        <v>8.21437931060791</v>
+        <v>8.21437835693359</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G825" t="n">
-        <v>8.25660133361816</v>
+        <v>8.25660037994385</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>8.75</v>
       </c>
       <c r="G826" t="n">
-        <v>8.20968723297119</v>
+        <v>8.20968818664551</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>8.13462734222412</v>
+        <v>8.1346263885498</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G831" t="n">
-        <v>8.13931751251221</v>
+        <v>8.13932037353516</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>8.04549407958984</v>
+        <v>8.04549312591553</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G834" t="n">
-        <v>8.18623065948486</v>
+        <v>8.1862325668335</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G835" t="n">
-        <v>8.24252605438232</v>
+        <v>8.24252510070801</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G836" t="n">
-        <v>8.2284517288208</v>
+        <v>8.22845363616943</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G838" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277313232422</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>8.0970983505249</v>
+        <v>8.09709739685059</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>8.38493251800537</v>
+        <v>8.38493156433105</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G845" t="n">
-        <v>8.36133861541748</v>
+        <v>8.36133766174316</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>8.98499965667725</v>
       </c>
       <c r="G846" t="n">
-        <v>8.47930240631104</v>
+        <v>8.47930335998535</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G847" t="n">
-        <v>8.31415176391602</v>
+        <v>8.31415271759033</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G849" t="n">
-        <v>8.3566198348999</v>
+        <v>8.35661888122559</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>8.54064559936523</v>
+        <v>8.54064464569092</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>8.68220138549805</v>
+        <v>8.68220329284668</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.125</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61142158508301</v>
+        <v>8.61142253875732</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G853" t="n">
-        <v>8.70107650756836</v>
+        <v>8.70107746124268</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G854" t="n">
-        <v>8.64445400238037</v>
+        <v>8.64445495605469</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G855" t="n">
-        <v>8.57839393615723</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G856" t="n">
-        <v>8.55480098724365</v>
+        <v>8.55479907989502</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>8.57367420196533</v>
+        <v>8.57367515563965</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.125</v>
       </c>
       <c r="G859" t="n">
-        <v>8.61142158508301</v>
+        <v>8.61142253875732</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G860" t="n">
-        <v>8.67748355865479</v>
+        <v>8.67748260498047</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>8.57839393615723</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>8.57367420196533</v>
+        <v>8.57367515563965</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>8.57367420196533</v>
+        <v>8.57367515563965</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G865" t="n">
-        <v>8.52177143096924</v>
+        <v>8.52177047729492</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G866" t="n">
-        <v>8.40852451324463</v>
+        <v>8.40852355957031</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G868" t="n">
-        <v>8.25281047821045</v>
+        <v>8.25280952453613</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G869" t="n">
-        <v>8.24809169769287</v>
+        <v>8.24809265136719</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G870" t="n">
-        <v>8.28112125396729</v>
+        <v>8.28112316131592</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G871" t="n">
-        <v>8.31415176391602</v>
+        <v>8.31415271759033</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G872" t="n">
-        <v>8.25281047821045</v>
+        <v>8.25280952453613</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G873" t="n">
-        <v>8.2858419418335</v>
+        <v>8.28584098815918</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G874" t="n">
-        <v>8.20090579986572</v>
+        <v>8.20090675354004</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G875" t="n">
-        <v>8.31415176391602</v>
+        <v>8.31415271759033</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G876" t="n">
-        <v>8.32830810546875</v>
+        <v>8.32830905914307</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G878" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696681976318</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G879" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>8.25281047821045</v>
+        <v>8.25280952453613</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>8.68220138549805</v>
+        <v>8.68220329284668</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G888" t="n">
-        <v>8.130126953125</v>
+        <v>8.13012790679932</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G890" t="n">
-        <v>8.34718227386475</v>
+        <v>8.34718322753906</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G891" t="n">
-        <v>8.52177143096924</v>
+        <v>8.52177047729492</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G892" t="n">
-        <v>8.3566198348999</v>
+        <v>8.35661888122559</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G893" t="n">
-        <v>8.30471515655518</v>
+        <v>8.30471611022949</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G894" t="n">
-        <v>8.32830810546875</v>
+        <v>8.32830905914307</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G896" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696681976318</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G897" t="n">
-        <v>8.24337291717529</v>
+        <v>8.24337196350098</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G898" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G899" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>8.17259502410889</v>
+        <v>8.17259407043457</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G902" t="n">
-        <v>8.15843963623047</v>
+        <v>8.15844058990479</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G905" t="n">
-        <v>8.04047584533691</v>
+        <v>8.04047393798828</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12540817260742</v>
+        <v>8.12540912628174</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G908" t="n">
-        <v>8.04991245269775</v>
+        <v>8.04991054534912</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.94610261917114</v>
+        <v>7.9461030960083</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G912" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779136657715</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>7.67242479324341</v>
+        <v>7.67242383956909</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>7.50727367401123</v>
+        <v>7.50727415084839</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>7.50255537033081</v>
+        <v>7.50255489349365</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G917" t="n">
-        <v>7.54502248764038</v>
+        <v>7.54502201080322</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>7.38930892944336</v>
+        <v>7.38930988311768</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G920" t="n">
-        <v>7.47896242141724</v>
+        <v>7.47896289825439</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>7.34684228897095</v>
+        <v>7.34684181213379</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.39874601364136</v>
+        <v>7.39874696731567</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G924" t="n">
-        <v>7.48368120193481</v>
+        <v>7.48368072509766</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G925" t="n">
-        <v>7.79038906097412</v>
+        <v>7.79039001464844</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>7.83285617828369</v>
+        <v>7.83285760879517</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G931" t="n">
-        <v>8.08294010162354</v>
+        <v>8.08294105529785</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G932" t="n">
-        <v>8.04519271850586</v>
+        <v>8.04519367218018</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>8.625</v>
       </c>
       <c r="G933" t="n">
-        <v>8.13956451416016</v>
+        <v>8.13956546783447</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.15843963623047</v>
+        <v>8.15844058990479</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G939" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779136657715</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G941" t="n">
-        <v>8.04519271850586</v>
+        <v>8.04519367218018</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>7.87532520294189</v>
+        <v>7.87532472610474</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G943" t="n">
-        <v>7.69129800796509</v>
+        <v>7.6912989616394</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>7.7951078414917</v>
+        <v>7.79510736465454</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G945" t="n">
-        <v>7.76679611206055</v>
+        <v>7.76679563522339</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G946" t="n">
-        <v>7.71017360687256</v>
+        <v>7.7101731300354</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G948" t="n">
-        <v>7.76679611206055</v>
+        <v>7.76679563522339</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G951" t="n">
-        <v>7.91779088973999</v>
+        <v>7.91779136657715</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>8.25</v>
       </c>
       <c r="G952" t="n">
-        <v>7.7856707572937</v>
+        <v>7.78567123413086</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>7.82341814041138</v>
+        <v>7.82341909408569</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G954" t="n">
-        <v>7.83285617828369</v>
+        <v>7.83285760879517</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G956" t="n">
-        <v>7.73848390579224</v>
+        <v>7.73848485946655</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G958" t="n">
-        <v>7.92251014709473</v>
+        <v>7.92251110076904</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G962" t="n">
-        <v>8.00744342803955</v>
+        <v>8.00744438171387</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G964" t="n">
-        <v>8.00744342803955</v>
+        <v>8.00744438171387</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G965" t="n">
-        <v>7.889479637146</v>
+        <v>7.88947916030884</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>7.63467597961426</v>
+        <v>7.63467645645142</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>7.52614831924438</v>
+        <v>7.52614879608154</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G971" t="n">
-        <v>7.57805252075195</v>
+        <v>7.57805156707764</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G972" t="n">
-        <v>7.71961116790771</v>
+        <v>7.7196102142334</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G973" t="n">
-        <v>7.71961116790771</v>
+        <v>7.7196102142334</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G975" t="n">
-        <v>7.69601774215698</v>
+        <v>7.69601678848267</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>7.75736045837402</v>
+        <v>7.75735998153687</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G979" t="n">
-        <v>7.87532520294189</v>
+        <v>7.87532472610474</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>7.83285617828369</v>
+        <v>7.83285760879517</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G981" t="n">
-        <v>7.75736045837402</v>
+        <v>7.75735998153687</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G982" t="n">
-        <v>7.80454587936401</v>
+        <v>7.80454540252686</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>7.77623319625854</v>
+        <v>7.77623271942139</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G984" t="n">
-        <v>7.73848390579224</v>
+        <v>7.73848485946655</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G985" t="n">
-        <v>7.73376560211182</v>
+        <v>7.7337646484375</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>7.74792242050171</v>
+        <v>7.74792289733887</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>7.86588621139526</v>
+        <v>7.86588478088379</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>7.86588621139526</v>
+        <v>7.86588478088379</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G989" t="n">
-        <v>7.7951078414917</v>
+        <v>7.79510736465454</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>7.83285617828369</v>
+        <v>7.83285760879517</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>7.80926322937012</v>
+        <v>7.80926370620728</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>7.98856782913208</v>
+        <v>7.98856973648071</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G996" t="n">
-        <v>7.92722749710083</v>
+        <v>7.92722797393799</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G998" t="n">
-        <v>7.66298818588257</v>
+        <v>7.66298723220825</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>7.71017360687256</v>
+        <v>7.7101731300354</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>7.71017360687256</v>
+        <v>7.7101731300354</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1002" t="n">
-        <v>7.73376560211182</v>
+        <v>7.7337646484375</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G1004" t="n">
-        <v>7.72432994842529</v>
+        <v>7.72432899475098</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1006" t="n">
-        <v>7.71961116790771</v>
+        <v>7.7196102142334</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1008" t="n">
-        <v>7.67714357376099</v>
+        <v>7.67714309692383</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>7.67714357376099</v>
+        <v>7.67714309692383</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1010" t="n">
-        <v>7.73376560211182</v>
+        <v>7.7337646484375</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>7.79038906097412</v>
+        <v>7.79039001464844</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>7.82813739776611</v>
+        <v>7.82813835144043</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G1014" t="n">
-        <v>7.79982614517212</v>
+        <v>7.79982709884644</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>7.66298818588257</v>
+        <v>7.66298723220825</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1017" t="n">
-        <v>7.71961116790771</v>
+        <v>7.7196102142334</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1018" t="n">
-        <v>7.69129800796509</v>
+        <v>7.6912989616394</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1019" t="n">
-        <v>7.59692764282227</v>
+        <v>7.59692811965942</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1020" t="n">
-        <v>7.65826892852783</v>
+        <v>7.65826988220215</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1022" t="n">
-        <v>7.65826892852783</v>
+        <v>7.65826988220215</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1023" t="n">
-        <v>7.65826892852783</v>
+        <v>7.65826988220215</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>7.74320411682129</v>
+        <v>7.74320363998413</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1025" t="n">
-        <v>7.80454587936401</v>
+        <v>7.80454540252686</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1026" t="n">
-        <v>7.9555401802063</v>
+        <v>7.95553970336914</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.12540817260742</v>
+        <v>8.12540912628174</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.17259502410889</v>
+        <v>8.17259407043457</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.2669677734375</v>
+        <v>8.26696681976318</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.38493251800537</v>
+        <v>8.38493156433105</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.32358932495117</v>
+        <v>8.32359027862549</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.35190010070801</v>
+        <v>8.35190105438232</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.42268085479736</v>
+        <v>8.42267990112305</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.46514797210693</v>
+        <v>8.46514701843262</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.51233386993408</v>
+        <v>8.5123348236084</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.55480098724365</v>
+        <v>8.55479907989502</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.52177143096924</v>
+        <v>8.52177047729492</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.46514797210693</v>
+        <v>8.46514701843262</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.40852451324463</v>
+        <v>8.40852355957031</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>8.98499965667725</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.47930240631104</v>
+        <v>8.47930335998535</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.1914701461792</v>
+        <v>8.19146919250488</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.04047584533691</v>
+        <v>8.04047393798828</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.06878566741943</v>
+        <v>8.06878662109375</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.6252384185791</v>
+        <v>7.62523889541626</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.58749055862427</v>
+        <v>7.58749008178711</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>7.33268594741821</v>
+        <v>7.33268642425537</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.11563110351562</v>
+        <v>7.11563014984131</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.068443775177</v>
+        <v>7.06844472885132</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.19112825393677</v>
+        <v>7.19112873077393</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.25247001647949</v>
+        <v>7.25246953964233</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.22887754440308</v>
+        <v>7.22887706756592</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.98822927474976</v>
+        <v>6.98822975158691</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.59658670425415</v>
+        <v>6.59658622741699</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.59658670425415</v>
+        <v>6.59658622741699</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.26628541946411</v>
+        <v>6.26628494262695</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>5.46412467956543</v>
+        <v>5.46412515640259</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1069" t="n">
-        <v>5.22347688674927</v>
+        <v>5.22347736358643</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1071" t="n">
-        <v>6.36065626144409</v>
+        <v>6.36065673828125</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.99260711669922</v>
+        <v>5.99260759353638</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.20494318008423</v>
+        <v>6.20494365692139</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.66736507415771</v>
+        <v>6.66736555099487</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1076" t="n">
-        <v>6.73814344406128</v>
+        <v>6.73814392089844</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.27572202682495</v>
+        <v>6.27572298049927</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.93787145614624</v>
+        <v>5.9378719329834</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.37799978256226</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.0190315246582</v>
+        <v>6.01903104782104</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.73400020599365</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.35499477386475</v>
+        <v>6.3549952507019</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.28515958786011</v>
+        <v>6.28515911102295</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.25684881210327</v>
+        <v>6.25684833526611</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.558837890625</v>
+        <v>6.55883741378784</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.72530555725098</v>
+        <v>6.72530603408813</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.85467529296875</v>
+        <v>6.85467481613159</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.33599996566772</v>
       </c>
       <c r="G1106" t="n">
-        <v>6.97833633422852</v>
+        <v>6.97833681106567</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>6.94399976730347</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.6054482460022</v>
+        <v>6.60544872283936</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>6.57310581207275</v>
+        <v>6.57310628890991</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>6.76399993896484</v>
       </c>
       <c r="G1113" t="n">
-        <v>6.4342246055603</v>
+        <v>6.43422412872314</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.56359434127808</v>
+        <v>6.56359338760376</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1117" t="n">
-        <v>6.61115646362305</v>
+        <v>6.61115598678589</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>6.83945465087891</v>
+        <v>6.83945512771606</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1122" t="n">
-        <v>6.99165439605713</v>
+        <v>6.99165391921997</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.39200019836426</v>
       </c>
       <c r="G1126" t="n">
-        <v>7.03160715103149</v>
+        <v>7.03160667419434</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>7.43200016021729</v>
       </c>
       <c r="G1127" t="n">
-        <v>7.06965684890747</v>
+        <v>7.06965732574463</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>6.95360374450684</v>
+        <v>6.95360469818115</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1130" t="n">
-        <v>6.96311712265015</v>
+        <v>6.96311664581299</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>7.57200002670288</v>
       </c>
       <c r="G1131" t="n">
-        <v>7.20283031463623</v>
+        <v>7.20283079147339</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>7.81599998474121</v>
       </c>
       <c r="G1143" t="n">
-        <v>7.43493461608887</v>
+        <v>7.43493509292603</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>7.71799993515015</v>
       </c>
       <c r="G1144" t="n">
-        <v>7.34171295166016</v>
+        <v>7.341712474823</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.59093904495239</v>
+        <v>7.59093952178955</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.72411346435547</v>
+        <v>7.72411298751831</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>8.14299964904785</v>
       </c>
       <c r="G1149" t="n">
-        <v>7.7459921836853</v>
+        <v>7.74599170684814</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>8.09200000762939</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.6974778175354</v>
+        <v>7.69747829437256</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>8.19400024414062</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.79450654983521</v>
+        <v>7.79450607299805</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>8.10599994659424</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.71079683303833</v>
+        <v>7.71079540252686</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>8.26799964904785</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.86489772796631</v>
+        <v>7.86489677429199</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>8.15200042724609</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.75455331802368</v>
+        <v>7.75455379486084</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>8.31099987030029</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.90580034255981</v>
+        <v>7.90580081939697</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.72599983215332</v>
       </c>
       <c r="G1162" t="n">
-        <v>8.30056667327881</v>
+        <v>8.30056858062744</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>8.51099967956543</v>
       </c>
       <c r="G1163" t="n">
-        <v>8.09605026245117</v>
+        <v>8.09605121612549</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>8.51299953460693</v>
       </c>
       <c r="G1164" t="n">
-        <v>8.09795188903809</v>
+        <v>8.09795093536377</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.15692901611328</v>
+        <v>8.1569299697876</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.17119789123535</v>
+        <v>8.17119884490967</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.09509944915771</v>
+        <v>8.0950984954834</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>8.55900001525879</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.14170932769775</v>
+        <v>8.14171028137207</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.3091287612915</v>
+        <v>8.30912780761719</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1173" t="n">
-        <v>8.27107810974121</v>
+        <v>8.27107906341553</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>8.57100009918213</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.15312480926514</v>
+        <v>8.15312385559082</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.15692901611328</v>
+        <v>8.1569299697876</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>8.63899993896484</v>
       </c>
       <c r="G1181" t="n">
-        <v>8.21780967712402</v>
+        <v>8.21781063079834</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>8.73299980163574</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.30722618103027</v>
+        <v>8.30722713470459</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G1183" t="n">
-        <v>8.18546772003174</v>
+        <v>8.18546581268311</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G1186" t="n">
-        <v>8.35574054718018</v>
+        <v>8.35574150085449</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.89099979400635</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.45752334594727</v>
+        <v>8.45752239227295</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.35193634033203</v>
+        <v>8.35193538665771</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.58308696746826</v>
+        <v>8.58308887481689</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.68867588043213</v>
+        <v>8.68867683410645</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.68867588043213</v>
+        <v>8.68867683410645</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1196" t="n">
-        <v>8.8132905960083</v>
+        <v>8.81328964233398</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>9.16699981689453</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.72006607055664</v>
+        <v>8.72006702423096</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.80567932128906</v>
+        <v>8.80568027496338</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.88082885742188</v>
+        <v>8.88082790374756</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.6734561920166</v>
+        <v>8.67345714569092</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>9.41100025177002</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.95217132568359</v>
+        <v>8.95217037200928</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G1207" t="n">
-        <v>8.86465740203857</v>
+        <v>8.86465644836426</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>9.36900043487549</v>
       </c>
       <c r="G1208" t="n">
-        <v>8.91221904754639</v>
+        <v>8.91221809387207</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G1209" t="n">
-        <v>8.91031646728516</v>
+        <v>8.91031551361084</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1213" t="n">
-        <v>8.83707141876221</v>
+        <v>8.83707046508789</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1214" t="n">
-        <v>8.90841388702393</v>
+        <v>8.90841484069824</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>9.0748815536499</v>
+        <v>9.07488250732422</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G1218" t="n">
-        <v>8.925537109375</v>
+        <v>8.92553615570068</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>9.44900035858154</v>
       </c>
       <c r="G1219" t="n">
-        <v>8.98831844329834</v>
+        <v>8.98831939697266</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>9.39799976348877</v>
       </c>
       <c r="G1221" t="n">
-        <v>8.93980407714844</v>
+        <v>8.93980598449707</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G1223" t="n">
-        <v>8.80092430114746</v>
+        <v>8.80092334747314</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>9.07800006866455</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.63540744781494</v>
+        <v>8.63540554046631</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>9.20600032806396</v>
       </c>
       <c r="G1233" t="n">
-        <v>8.75716686248779</v>
+        <v>8.75716590881348</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G1235" t="n">
-        <v>9.10722351074219</v>
+        <v>9.1072244644165</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.12244510650635</v>
+        <v>9.12244606018066</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>9.62800025939941</v>
       </c>
       <c r="G1239" t="n">
-        <v>9.15859127044678</v>
+        <v>9.15859222412109</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>9.57800006866455</v>
       </c>
       <c r="G1243" t="n">
-        <v>9.11102867126465</v>
+        <v>9.11102962493896</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>9.45600032806396</v>
       </c>
       <c r="G1244" t="n">
-        <v>8.99497699737549</v>
+        <v>8.9949779510498</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1247" t="n">
-        <v>9.05585765838623</v>
+        <v>9.05585670471191</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1251" t="n">
-        <v>8.9892692565918</v>
+        <v>8.98927021026611</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G1257" t="n">
-        <v>8.86941242218018</v>
+        <v>8.86941432952881</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>8.99878215789795</v>
+        <v>8.99878311157227</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>9.36600017547607</v>
       </c>
       <c r="G1260" t="n">
-        <v>8.9093656539917</v>
+        <v>8.90936470031738</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1261" t="n">
-        <v>8.70389461517334</v>
+        <v>8.70389652252197</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>8.73623847961426</v>
+        <v>8.73623943328857</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G1267" t="n">
-        <v>8.74765396118164</v>
+        <v>8.74765300750732</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>9.46199989318848</v>
       </c>
       <c r="G1269" t="n">
-        <v>9.00068378448486</v>
+        <v>9.00068473815918</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1270" t="n">
-        <v>8.88463306427002</v>
+        <v>8.88463401794434</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.77048301696777</v>
+        <v>8.77048397064209</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>8.97200012207031</v>
       </c>
       <c r="G1272" t="n">
-        <v>8.53457450866699</v>
+        <v>8.53457546234131</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G1274" t="n">
-        <v>8.41281509399414</v>
+        <v>8.41281414031982</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1276" t="n">
-        <v>8.29485988616943</v>
+        <v>8.29486083984375</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>8.67800045013428</v>
       </c>
       <c r="G1277" t="n">
-        <v>8.25490951538086</v>
+        <v>8.25490856170654</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>8.72200012207031</v>
       </c>
       <c r="G1279" t="n">
-        <v>8.29676342010498</v>
+        <v>8.29676246643066</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1281" t="n">
-        <v>8.41852283477783</v>
+        <v>8.41852188110352</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>8.79399967193604</v>
       </c>
       <c r="G1282" t="n">
-        <v>8.3652515411377</v>
+        <v>8.36525249481201</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G1283" t="n">
-        <v>8.35574054718018</v>
+        <v>8.35574150085449</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1284" t="n">
-        <v>8.45657348632812</v>
+        <v>8.45657253265381</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>8.80799961090088</v>
       </c>
       <c r="G1286" t="n">
-        <v>8.37856960296631</v>
+        <v>8.37856864929199</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G1287" t="n">
-        <v>8.5060396194458</v>
+        <v>8.50603866577148</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1288" t="n">
-        <v>8.46608448028564</v>
+        <v>8.46608352661133</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G1290" t="n">
-        <v>8.4432544708252</v>
+        <v>8.44325542449951</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>8.88199996948242</v>
       </c>
       <c r="G1291" t="n">
-        <v>8.44896125793457</v>
+        <v>8.44896221160889</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1292" t="n">
-        <v>8.69438362121582</v>
+        <v>8.69438457489014</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>9.18200016021729</v>
       </c>
       <c r="G1293" t="n">
-        <v>8.73433589935303</v>
+        <v>8.73433494567871</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>9.67599964141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>9.20425128936768</v>
+        <v>9.20425033569336</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G1299" t="n">
-        <v>9.2442045211792</v>
+        <v>9.24420356750488</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1300" t="n">
-        <v>9.30317974090576</v>
+        <v>9.30318069458008</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>9.76399993896484</v>
       </c>
       <c r="G1303" t="n">
-        <v>9.28796100616455</v>
+        <v>9.28796005249023</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G1304" t="n">
-        <v>9.29937648773193</v>
+        <v>9.29937553405762</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G1306" t="n">
-        <v>9.06727123260498</v>
+        <v>9.0672721862793</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G1308" t="n">
-        <v>9.17571449279785</v>
+        <v>9.17571353912354</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1313" t="n">
-        <v>8.91316986083984</v>
+        <v>8.91316890716553</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1316" t="n">
-        <v>9.22708225250244</v>
+        <v>9.22708034515381</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>9.86200046539307</v>
       </c>
       <c r="G1317" t="n">
-        <v>9.38118457794189</v>
+        <v>9.38118362426758</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>9.80399990081787</v>
       </c>
       <c r="G1320" t="n">
-        <v>9.32601165771484</v>
+        <v>9.32600975036621</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1321" t="n">
-        <v>9.24610614776611</v>
+        <v>9.24610710144043</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G1324" t="n">
-        <v>9.22327423095703</v>
+        <v>9.22327613830566</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>9.58800029754639</v>
       </c>
       <c r="G1326" t="n">
-        <v>9.12054252624512</v>
+        <v>9.1205415725708</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1327" t="n">
-        <v>9.10341835021973</v>
+        <v>9.10341930389404</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>9.59200000762939</v>
       </c>
       <c r="G1329" t="n">
-        <v>9.12434673309326</v>
+        <v>9.12434577941895</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>9.67599964141846</v>
       </c>
       <c r="G1331" t="n">
-        <v>9.20425128936768</v>
+        <v>9.20425033569336</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G1332" t="n">
-        <v>9.20995903015137</v>
+        <v>9.20995998382568</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>9.73200035095215</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.25752067565918</v>
+        <v>9.2575216293335</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1336" t="n">
-        <v>9.18903160095215</v>
+        <v>9.18903064727783</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>9.75</v>
       </c>
       <c r="G1338" t="n">
-        <v>9.27464389801025</v>
+        <v>9.27464294433594</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.20995903015137</v>
+        <v>9.20995998382568</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.42113590240479</v>
+        <v>9.42113494873047</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>9.98600006103516</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.49913597106934</v>
+        <v>9.49913787841797</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G1346" t="n">
-        <v>9.58905029296875</v>
+        <v>9.58904933929443</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>10.125</v>
       </c>
       <c r="G1347" t="n">
-        <v>9.68470191955566</v>
+        <v>9.68470096588135</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>9.99199962615967</v>
       </c>
       <c r="G1349" t="n">
-        <v>9.55748462677002</v>
+        <v>9.5574836730957</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.89400005340576</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.46374607086182</v>
+        <v>9.46374702453613</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>9.89400005340576</v>
       </c>
       <c r="G1352" t="n">
-        <v>9.46374607086182</v>
+        <v>9.46374702453613</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>9.8120002746582</v>
       </c>
       <c r="G1353" t="n">
-        <v>9.38531303405762</v>
+        <v>9.3853120803833</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>9.48861503601074</v>
+        <v>9.48861598968506</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.7325267791748</v>
+        <v>9.73252582550049</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.79470062255859</v>
+        <v>9.79469966888428</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.62730884552002</v>
+        <v>9.62730979919434</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>10.1149997711182</v>
       </c>
       <c r="G1362" t="n">
-        <v>9.67513656616211</v>
+        <v>9.67513561248779</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.65122318267822</v>
+        <v>9.65122222900391</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>10.3649997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.91426467895508</v>
+        <v>9.91426372528076</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.081654548645</v>
+        <v>10.0816535949707</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.99556732177734</v>
+        <v>9.99556827545166</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.1246976852417</v>
+        <v>10.1246967315674</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.1199140548706</v>
+        <v>10.1199150085449</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1380" t="n">
-        <v>10.4738254547119</v>
+        <v>10.4738245010376</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G1381" t="n">
-        <v>10.6507806777954</v>
+        <v>10.6507797241211</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>11.1049995422363</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.6220836639404</v>
+        <v>10.6220846176147</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G1393" t="n">
-        <v>10.9090375900269</v>
+        <v>10.9090385437012</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1394" t="n">
-        <v>10.8946905136108</v>
+        <v>10.8946914672852</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>11.2950000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>10.803822517395</v>
+        <v>10.8038215637207</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1397" t="n">
-        <v>10.8946905136108</v>
+        <v>10.8946914672852</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G1399" t="n">
-        <v>10.746431350708</v>
+        <v>10.7464303970337</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>10.6651268005371</v>
+        <v>10.6651277542114</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G1407" t="n">
-        <v>10.7033882141113</v>
+        <v>10.703387260437</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1409" t="n">
-        <v>10.4929542541504</v>
+        <v>10.4929552078247</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G1410" t="n">
-        <v>10.5551280975342</v>
+        <v>10.5551271438599</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>10.6651268005371</v>
+        <v>10.6651277542114</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1413" t="n">
-        <v>10.9951248168945</v>
+        <v>10.9951257705688</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.2294702529907</v>
+        <v>11.229471206665</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.2964277267456</v>
+        <v>11.2964267730713</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.3442516326904</v>
+        <v>11.3442525863647</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>11.9250001907349</v>
       </c>
       <c r="G1423" t="n">
-        <v>11.4064254760742</v>
+        <v>11.4064264297485</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1427" t="n">
-        <v>11.5451202392578</v>
+        <v>11.5451192855835</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>12.2150001525879</v>
       </c>
       <c r="G1428" t="n">
-        <v>11.6838140487671</v>
+        <v>11.6838150024414</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>11.5690336227417</v>
+        <v>11.5690326690674</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>11.914999961853</v>
       </c>
       <c r="G1444" t="n">
-        <v>11.3968601226807</v>
+        <v>11.396861076355</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1446" t="n">
-        <v>11.4016427993774</v>
+        <v>11.4016437530518</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1447" t="n">
-        <v>11.339469909668</v>
+        <v>11.3394680023193</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1449" t="n">
-        <v>11.339469909668</v>
+        <v>11.3394680023193</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>11.9250001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>11.4064254760742</v>
+        <v>11.4064264297485</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>12.2150001525879</v>
       </c>
       <c r="G1455" t="n">
-        <v>11.6838140487671</v>
+        <v>11.6838150024414</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>11.7699022293091</v>
+        <v>11.7699012756348</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1458" t="n">
-        <v>11.6168603897095</v>
+        <v>11.6168594360352</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1464" t="n">
-        <v>11.5690336227417</v>
+        <v>11.5690326690674</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1465" t="n">
-        <v>11.7459888458252</v>
+        <v>11.7459878921509</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>12.375</v>
       </c>
       <c r="G1467" t="n">
-        <v>11.8368558883667</v>
+        <v>11.836856842041</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>12.414999961853</v>
       </c>
       <c r="G1468" t="n">
-        <v>11.8751182556152</v>
+        <v>11.8751173019409</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.004246711731</v>
+        <v>12.0042476654053</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1471" t="n">
-        <v>11.9659862518311</v>
+        <v>11.9659852981567</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>12.7550001144409</v>
       </c>
       <c r="G1472" t="n">
-        <v>12.2003316879272</v>
+        <v>12.2003326416016</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1473" t="n">
-        <v>12.3677225112915</v>
+        <v>12.3677215576172</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1476" t="n">
-        <v>12.3677225112915</v>
+        <v>12.3677215576172</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>12.9049997329712</v>
       </c>
       <c r="G1478" t="n">
-        <v>12.3438081741333</v>
+        <v>12.3438100814819</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1479" t="n">
-        <v>12.3772869110107</v>
+        <v>12.3772859573364</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1481" t="n">
-        <v>11.7555532455444</v>
+        <v>11.7555541992188</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1482" t="n">
-        <v>11.8320741653442</v>
+        <v>11.8320732116699</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1483" t="n">
-        <v>11.7459888458252</v>
+        <v>11.7459878921509</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>12.4350004196167</v>
       </c>
       <c r="G1484" t="n">
-        <v>11.8942470550537</v>
+        <v>11.8942489624023</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>12.5349998474121</v>
       </c>
       <c r="G1485" t="n">
-        <v>11.9898977279663</v>
+        <v>11.9898986816406</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1490" t="n">
-        <v>12.2242450714111</v>
+        <v>12.2242441177368</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1492" t="n">
-        <v>12.2290267944336</v>
+        <v>12.2290277481079</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1494" t="n">
-        <v>12.4538097381592</v>
+        <v>12.4538087844849</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>12.7694568634033</v>
+        <v>12.7694578170776</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>13.3450002670288</v>
       </c>
       <c r="G1497" t="n">
-        <v>12.7646751403809</v>
+        <v>12.7646760940552</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G1498" t="n">
-        <v>12.7455434799194</v>
+        <v>12.7455444335938</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1501" t="n">
-        <v>12.4059829711914</v>
+        <v>12.4059839248657</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G1503" t="n">
-        <v>12.2959833145142</v>
+        <v>12.2959823608398</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1505" t="n">
-        <v>12.3103303909302</v>
+        <v>12.3103313446045</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1507" t="n">
-        <v>12.1572885513306</v>
+        <v>12.1572895050049</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>13.2550001144409</v>
       </c>
       <c r="G1510" t="n">
-        <v>12.6785888671875</v>
+        <v>12.6785898208618</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1511" t="n">
-        <v>12.4059829711914</v>
+        <v>12.4059839248657</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>12.9849996566772</v>
       </c>
       <c r="G1512" t="n">
-        <v>12.4203290939331</v>
+        <v>12.4203300476074</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.3964166641235</v>
+        <v>12.3964176177979</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1514" t="n">
-        <v>12.3677225112915</v>
+        <v>12.3677215576172</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1517" t="n">
-        <v>12.3007659912109</v>
+        <v>12.3007669448853</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1525" t="n">
-        <v>12.3103303909302</v>
+        <v>12.3103313446045</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G1526" t="n">
-        <v>12.2959833145142</v>
+        <v>12.2959823608398</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1528" t="n">
-        <v>12.3103303909302</v>
+        <v>12.3103313446045</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>12.21946144104</v>
+        <v>12.2194623947144</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1533" t="n">
-        <v>11.4972944259644</v>
+        <v>11.4972953796387</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G1536" t="n">
-        <v>10.985559463501</v>
+        <v>10.9855604171753</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>11.3950004577637</v>
       </c>
       <c r="G1541" t="n">
-        <v>10.8994750976562</v>
+        <v>10.8994741439819</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.6507806777954</v>
+        <v>10.6507797241211</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1544" t="n">
-        <v>10.4833908081055</v>
+        <v>10.4833898544312</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G1546" t="n">
-        <v>10.3590421676636</v>
+        <v>10.3590431213379</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1547" t="n">
-        <v>10.6077375411987</v>
+        <v>10.6077365875244</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G1549" t="n">
-        <v>10.9090375900269</v>
+        <v>10.9090385437012</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G1550" t="n">
-        <v>10.6986055374146</v>
+        <v>10.6986045837402</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>10.3686084747314</v>
+        <v>10.3686075210571</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1553" t="n">
-        <v>10.2920875549316</v>
+        <v>10.2920866012573</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>10.3303489685059</v>
+        <v>10.3303480148315</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>10.4849996566772</v>
       </c>
       <c r="G1558" t="n">
-        <v>10.0290460586548</v>
+        <v>10.0290451049805</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>10.4949998855591</v>
       </c>
       <c r="G1560" t="n">
-        <v>10.0386095046997</v>
+        <v>10.0386114120483</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>10.2550001144409</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.80904769897461</v>
+        <v>9.80904865264893</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.88983726501465</v>
+        <v>8.88983821868896</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>9.46199989318848</v>
       </c>
       <c r="G1565" t="n">
-        <v>9.0505313873291</v>
+        <v>9.05053234100342</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>9.8120002746582</v>
       </c>
       <c r="G1566" t="n">
-        <v>9.38531303405762</v>
+        <v>9.3853120803833</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.90705490112305</v>
+        <v>8.90705585479736</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>9.33199977874756</v>
       </c>
       <c r="G1570" t="n">
-        <v>8.92618560791016</v>
+        <v>8.92618465423584</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G1572" t="n">
-        <v>8.70618724822998</v>
+        <v>8.70618915557861</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>8.79800033569336</v>
       </c>
       <c r="G1573" t="n">
-        <v>8.41540622711182</v>
+        <v>8.41540718078613</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>9.41600036621094</v>
       </c>
       <c r="G1574" t="n">
-        <v>9.00653266906738</v>
+        <v>9.0065336227417</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.81905651092529</v>
+        <v>8.81905555725098</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G1577" t="n">
-        <v>8.86305522918701</v>
+        <v>8.86305618286133</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1578" t="n">
-        <v>8.8955774307251</v>
+        <v>8.89557838439941</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>9.60339736938477</v>
+        <v>9.60339641571045</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.49244117736816</v>
+        <v>9.49244213104248</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.48096466064453</v>
+        <v>9.4809627532959</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>10.2550001144409</v>
       </c>
       <c r="G1586" t="n">
-        <v>9.80904769897461</v>
+        <v>9.80904865264893</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.92861270904541</v>
+        <v>9.92861175537109</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>10.5649995803833</v>
       </c>
       <c r="G1588" t="n">
-        <v>10.1055669784546</v>
+        <v>10.1055660247803</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G1589" t="n">
-        <v>10.1246976852417</v>
+        <v>10.1246967315674</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>10.5550003051758</v>
       </c>
       <c r="G1590" t="n">
-        <v>10.0960025787354</v>
+        <v>10.096001625061</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G1591" t="n">
-        <v>10.2633905410767</v>
+        <v>10.263391494751</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G1592" t="n">
-        <v>10.2633905410767</v>
+        <v>10.263391494751</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.4833908081055</v>
+        <v>10.4833898544312</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>10.6949996948242</v>
       </c>
       <c r="G1594" t="n">
-        <v>10.2299127578735</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1595" t="n">
-        <v>10.34947681427</v>
+        <v>10.3494777679443</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>10.7449998855591</v>
       </c>
       <c r="G1596" t="n">
-        <v>10.2777395248413</v>
+        <v>10.277738571167</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>10.5550003051758</v>
       </c>
       <c r="G1600" t="n">
-        <v>10.0960025787354</v>
+        <v>10.096001625061</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>6.42000007629395</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>7964342</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>6.51800012588501</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>6.41200017929077</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>6.48400020599365</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>6.48600006103516</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>6.48600006103516</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>
